--- a/data/nzd0527/nzd0527.xlsx
+++ b/data/nzd0527/nzd0527.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T440"/>
+  <dimension ref="A1:T441"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29468,6 +29468,72 @@
         <v>328.71</v>
       </c>
       <c r="T440" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-23 22:15:01+00:00</t>
+        </is>
+      </c>
+      <c r="B441" t="n">
+        <v>310.11</v>
+      </c>
+      <c r="C441" t="n">
+        <v>302.18</v>
+      </c>
+      <c r="D441" t="n">
+        <v>301.21</v>
+      </c>
+      <c r="E441" t="n">
+        <v>311.99</v>
+      </c>
+      <c r="F441" t="n">
+        <v>324.29</v>
+      </c>
+      <c r="G441" t="n">
+        <v>324.24</v>
+      </c>
+      <c r="H441" t="n">
+        <v>326.16</v>
+      </c>
+      <c r="I441" t="n">
+        <v>318.28</v>
+      </c>
+      <c r="J441" t="n">
+        <v>326.19</v>
+      </c>
+      <c r="K441" t="n">
+        <v>336.8</v>
+      </c>
+      <c r="L441" t="n">
+        <v>338.91</v>
+      </c>
+      <c r="M441" t="n">
+        <v>335.7</v>
+      </c>
+      <c r="N441" t="n">
+        <v>331.65</v>
+      </c>
+      <c r="O441" t="n">
+        <v>324.23</v>
+      </c>
+      <c r="P441" t="n">
+        <v>323.35</v>
+      </c>
+      <c r="Q441" t="n">
+        <v>321.17</v>
+      </c>
+      <c r="R441" t="n">
+        <v>323.35</v>
+      </c>
+      <c r="S441" t="n">
+        <v>329.3</v>
+      </c>
+      <c r="T441" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -29484,7 +29550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B451"/>
+  <dimension ref="A1:B452"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33997,6 +34063,16 @@
       </c>
       <c r="B451" t="n">
         <v>-0.17</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>2025-12-23 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B452" t="n">
+        <v>-0.48</v>
       </c>
     </row>
   </sheetData>
@@ -34165,28 +34241,28 @@
         <v>0.0503</v>
       </c>
       <c r="I2" t="n">
-        <v>0.726253087697888</v>
+        <v>0.7173379518758525</v>
       </c>
       <c r="J2" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="K2" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2190623340742806</v>
+        <v>0.214352622216014</v>
       </c>
       <c r="M2" t="n">
-        <v>7.791037332422389</v>
+        <v>7.818410531889221</v>
       </c>
       <c r="N2" t="n">
-        <v>103.6491400956242</v>
+        <v>104.2644529065157</v>
       </c>
       <c r="O2" t="n">
-        <v>10.18082217188888</v>
+        <v>10.21099666567939</v>
       </c>
       <c r="P2" t="n">
-        <v>310.3949667022011</v>
+        <v>310.4862115307633</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34243,28 +34319,28 @@
         <v>0.0789</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6607899026465862</v>
+        <v>0.648539989743412</v>
       </c>
       <c r="J3" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="K3" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="L3" t="n">
-        <v>0.108057570479409</v>
+        <v>0.1042300607997428</v>
       </c>
       <c r="M3" t="n">
-        <v>10.63772324919316</v>
+        <v>10.68457162371297</v>
       </c>
       <c r="N3" t="n">
-        <v>198.6778635897934</v>
+        <v>199.8328125172541</v>
       </c>
       <c r="O3" t="n">
-        <v>14.09531353286593</v>
+        <v>14.13622341777513</v>
       </c>
       <c r="P3" t="n">
-        <v>311.4476388277299</v>
+        <v>311.5730145062462</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34321,28 +34397,28 @@
         <v>0.075</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8067503606331488</v>
+        <v>0.7922026393908923</v>
       </c>
       <c r="J4" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="K4" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1230844479765032</v>
+        <v>0.1188224855487793</v>
       </c>
       <c r="M4" t="n">
-        <v>11.90372817185181</v>
+        <v>11.9661196861725</v>
       </c>
       <c r="N4" t="n">
-        <v>255.6077320223217</v>
+        <v>257.2925024030642</v>
       </c>
       <c r="O4" t="n">
-        <v>15.98773692622948</v>
+        <v>16.04033984686934</v>
       </c>
       <c r="P4" t="n">
-        <v>311.6409444302246</v>
+        <v>311.7898377681635</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34399,28 +34475,28 @@
         <v>0.0822</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7632453719397154</v>
+        <v>0.7515982626284892</v>
       </c>
       <c r="J5" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="K5" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="L5" t="n">
-        <v>0.15860571569436</v>
+        <v>0.1541062012268706</v>
       </c>
       <c r="M5" t="n">
-        <v>9.31853960162514</v>
+        <v>9.364718935458695</v>
       </c>
       <c r="N5" t="n">
-        <v>170.3531399864065</v>
+        <v>171.4182465466692</v>
       </c>
       <c r="O5" t="n">
-        <v>13.05194008515234</v>
+        <v>13.09267912028204</v>
       </c>
       <c r="P5" t="n">
-        <v>317.245582327096</v>
+        <v>317.3647884181263</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34477,28 +34553,28 @@
         <v>0.0634</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7866555283761251</v>
+        <v>0.7786895432117507</v>
       </c>
       <c r="J6" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="K6" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2234052509958147</v>
+        <v>0.2197905411390033</v>
       </c>
       <c r="M6" t="n">
-        <v>7.833858818408609</v>
+        <v>7.855271961386316</v>
       </c>
       <c r="N6" t="n">
-        <v>119.3014542255523</v>
+        <v>119.7135007035847</v>
       </c>
       <c r="O6" t="n">
-        <v>10.92252050698703</v>
+        <v>10.94136649160354</v>
       </c>
       <c r="P6" t="n">
-        <v>320.92578382483</v>
+        <v>321.0071522549195</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -34555,28 +34631,28 @@
         <v>0.0667</v>
       </c>
       <c r="I7" t="n">
-        <v>1.275840899160595</v>
+        <v>1.266111111168453</v>
       </c>
       <c r="J7" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="K7" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3557128829578052</v>
+        <v>0.3519593487442014</v>
       </c>
       <c r="M7" t="n">
-        <v>9.613310729517476</v>
+        <v>9.650583939986173</v>
       </c>
       <c r="N7" t="n">
-        <v>163.5115213853958</v>
+        <v>164.159347423705</v>
       </c>
       <c r="O7" t="n">
-        <v>12.78716236642813</v>
+        <v>12.81246843600814</v>
       </c>
       <c r="P7" t="n">
-        <v>311.8321151780322</v>
+        <v>311.9314999443465</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -34633,28 +34709,28 @@
         <v>0.06909999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>1.044315044000364</v>
+        <v>1.037987124786716</v>
       </c>
       <c r="J8" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="K8" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3106642229484727</v>
+        <v>0.3084755487628239</v>
       </c>
       <c r="M8" t="n">
-        <v>8.886481443060774</v>
+        <v>8.902711771093436</v>
       </c>
       <c r="N8" t="n">
-        <v>134.2079098878906</v>
+        <v>134.333076392873</v>
       </c>
       <c r="O8" t="n">
-        <v>11.58481376146766</v>
+        <v>11.59021468277758</v>
       </c>
       <c r="P8" t="n">
-        <v>312.4402975246428</v>
+        <v>312.5049339558592</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -34711,28 +34787,28 @@
         <v>0.0717</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8869522043841962</v>
+        <v>0.8784250021856113</v>
       </c>
       <c r="J9" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="K9" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2424217592428332</v>
+        <v>0.2387791985293228</v>
       </c>
       <c r="M9" t="n">
-        <v>9.044383917327275</v>
+        <v>9.074132887830705</v>
       </c>
       <c r="N9" t="n">
-        <v>136.3426701318822</v>
+        <v>136.8156463805499</v>
       </c>
       <c r="O9" t="n">
-        <v>11.67658640750293</v>
+        <v>11.69682206330206</v>
       </c>
       <c r="P9" t="n">
-        <v>313.4982894920796</v>
+        <v>313.5853904647323</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -34789,28 +34865,28 @@
         <v>0.0781</v>
       </c>
       <c r="I10" t="n">
-        <v>0.9991411187442025</v>
+        <v>0.9910044051475331</v>
       </c>
       <c r="J10" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="K10" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="L10" t="n">
-        <v>0.3157634876760372</v>
+        <v>0.3120658313077951</v>
       </c>
       <c r="M10" t="n">
-        <v>7.870299935095681</v>
+        <v>7.89906976235139</v>
       </c>
       <c r="N10" t="n">
-        <v>119.970222985633</v>
+        <v>120.4104178931329</v>
       </c>
       <c r="O10" t="n">
-        <v>10.95309193724005</v>
+        <v>10.9731680882566</v>
       </c>
       <c r="P10" t="n">
-        <v>317.6016068673912</v>
+        <v>317.6847192003654</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -34867,28 +34943,28 @@
         <v>0.06270000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>1.520649733619103</v>
+        <v>1.507781438126072</v>
       </c>
       <c r="J11" t="n">
+        <v>440</v>
+      </c>
+      <c r="K11" t="n">
         <v>439</v>
       </c>
-      <c r="K11" t="n">
-        <v>438</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.3349831477569618</v>
+        <v>0.3307964757791969</v>
       </c>
       <c r="M11" t="n">
-        <v>11.62378174490614</v>
+        <v>11.67918693055288</v>
       </c>
       <c r="N11" t="n">
-        <v>253.5553842852994</v>
+        <v>254.7555138056466</v>
       </c>
       <c r="O11" t="n">
-        <v>15.92342250539435</v>
+        <v>15.96106242722102</v>
       </c>
       <c r="P11" t="n">
-        <v>324.7729138171396</v>
+        <v>324.9045359188217</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -34945,28 +35021,28 @@
         <v>0.1014</v>
       </c>
       <c r="I12" t="n">
-        <v>1.545137797927708</v>
+        <v>1.529630989478639</v>
       </c>
       <c r="J12" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="K12" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="L12" t="n">
-        <v>0.3022290047231234</v>
+        <v>0.2973008457401042</v>
       </c>
       <c r="M12" t="n">
-        <v>12.2591482076121</v>
+        <v>12.33204269102901</v>
       </c>
       <c r="N12" t="n">
-        <v>303.845119881608</v>
+        <v>305.7288484730018</v>
       </c>
       <c r="O12" t="n">
-        <v>17.43115371630943</v>
+        <v>17.48510361630728</v>
       </c>
       <c r="P12" t="n">
-        <v>331.9714062538658</v>
+        <v>332.130115678683</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -35023,28 +35099,28 @@
         <v>0.0926</v>
       </c>
       <c r="I13" t="n">
-        <v>1.56318332770845</v>
+        <v>1.54349169786216</v>
       </c>
       <c r="J13" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="K13" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2833871469079435</v>
+        <v>0.2768648643488367</v>
       </c>
       <c r="M13" t="n">
-        <v>13.31548052470356</v>
+        <v>13.408456696901</v>
       </c>
       <c r="N13" t="n">
-        <v>340.6162267773832</v>
+        <v>343.9933139590079</v>
       </c>
       <c r="O13" t="n">
-        <v>18.45579114471616</v>
+        <v>18.54705674653011</v>
       </c>
       <c r="P13" t="n">
-        <v>337.4022394168693</v>
+        <v>337.6037797439382</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -35101,28 +35177,28 @@
         <v>0.1059</v>
       </c>
       <c r="I14" t="n">
-        <v>1.492645105148499</v>
+        <v>1.471764719648093</v>
       </c>
       <c r="J14" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="K14" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2203191490747068</v>
+        <v>0.2145796228965378</v>
       </c>
       <c r="M14" t="n">
-        <v>15.62726086121316</v>
+        <v>15.72696142032074</v>
       </c>
       <c r="N14" t="n">
-        <v>434.6291044904692</v>
+        <v>438.3088604566526</v>
       </c>
       <c r="O14" t="n">
-        <v>20.84776017922475</v>
+        <v>20.93582719781219</v>
       </c>
       <c r="P14" t="n">
-        <v>337.8036776428925</v>
+        <v>338.0173846725251</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -35179,28 +35255,28 @@
         <v>0.0788</v>
       </c>
       <c r="I15" t="n">
-        <v>1.489129988931677</v>
+        <v>1.467729555682154</v>
       </c>
       <c r="J15" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="K15" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1861708387230425</v>
+        <v>0.1812294171578087</v>
       </c>
       <c r="M15" t="n">
-        <v>17.4669577664861</v>
+        <v>17.56791584106881</v>
       </c>
       <c r="N15" t="n">
-        <v>534.3525326583925</v>
+        <v>538.0410401594196</v>
       </c>
       <c r="O15" t="n">
-        <v>23.11606654814769</v>
+        <v>23.19571167607107</v>
       </c>
       <c r="P15" t="n">
-        <v>331.6071980717609</v>
+        <v>331.8262276975557</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -35257,28 +35333,28 @@
         <v>0.0936</v>
       </c>
       <c r="I16" t="n">
-        <v>1.578720285177079</v>
+        <v>1.556592554180257</v>
       </c>
       <c r="J16" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="K16" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1913697488757219</v>
+        <v>0.1864531104102213</v>
       </c>
       <c r="M16" t="n">
-        <v>18.05357226827782</v>
+        <v>18.16406131085277</v>
       </c>
       <c r="N16" t="n">
-        <v>580.5346367892581</v>
+        <v>584.4571028502604</v>
       </c>
       <c r="O16" t="n">
-        <v>24.09428639302808</v>
+        <v>24.1755476225516</v>
       </c>
       <c r="P16" t="n">
-        <v>329.9497028631926</v>
+        <v>330.176176251998</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -35335,28 +35411,28 @@
         <v>0.08169999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>1.956438080891509</v>
+        <v>1.93227833474697</v>
       </c>
       <c r="J17" t="n">
+        <v>440</v>
+      </c>
+      <c r="K17" t="n">
         <v>439</v>
       </c>
-      <c r="K17" t="n">
-        <v>438</v>
-      </c>
       <c r="L17" t="n">
-        <v>0.2672333959092417</v>
+        <v>0.2613137603802033</v>
       </c>
       <c r="M17" t="n">
-        <v>17.99329602619716</v>
+        <v>18.11681008026367</v>
       </c>
       <c r="N17" t="n">
-        <v>576.1596158025903</v>
+        <v>581.0616884067582</v>
       </c>
       <c r="O17" t="n">
-        <v>24.00332509888141</v>
+        <v>24.10522118560123</v>
       </c>
       <c r="P17" t="n">
-        <v>322.0428030015322</v>
+        <v>322.2909522596114</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -35413,28 +35489,28 @@
         <v>0.1195</v>
       </c>
       <c r="I18" t="n">
-        <v>2.010357390403993</v>
+        <v>1.986456056883918</v>
       </c>
       <c r="J18" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="K18" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="L18" t="n">
-        <v>0.3095660446957357</v>
+        <v>0.3029731315481662</v>
       </c>
       <c r="M18" t="n">
-        <v>16.84632359609816</v>
+        <v>16.97641535960408</v>
       </c>
       <c r="N18" t="n">
-        <v>496.8856166361584</v>
+        <v>501.8721717898925</v>
       </c>
       <c r="O18" t="n">
-        <v>22.29093126444381</v>
+        <v>22.40250369467423</v>
       </c>
       <c r="P18" t="n">
-        <v>322.4431840423781</v>
+        <v>322.687809937371</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -35491,28 +35567,28 @@
         <v>0.1194</v>
       </c>
       <c r="I19" t="n">
-        <v>1.894307507015336</v>
+        <v>1.871472697254574</v>
       </c>
       <c r="J19" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="K19" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="L19" t="n">
-        <v>0.3052095014385888</v>
+        <v>0.2985807982989666</v>
       </c>
       <c r="M19" t="n">
-        <v>15.99917578082025</v>
+        <v>16.12009078285792</v>
       </c>
       <c r="N19" t="n">
-        <v>450.2957441212961</v>
+        <v>454.8545614119664</v>
       </c>
       <c r="O19" t="n">
-        <v>21.22017304645031</v>
+        <v>21.32731960214331</v>
       </c>
       <c r="P19" t="n">
-        <v>329.1257329847966</v>
+        <v>329.3594431989161</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -35550,7 +35626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T440"/>
+  <dimension ref="A1:T441"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -80365,6 +80441,108 @@
         </is>
       </c>
     </row>
+    <row r="441">
+      <c r="A441" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-23 22:15:01+00:00</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>-46.30615583286073,169.90812226572515</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>-46.30643077848107,169.90731352079735</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>-46.306759226314696,169.90655165434768</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>-46.307178000031115,169.90586892768403</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>-46.30760845727582,169.90519643810592</t>
+        </is>
+      </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>-46.3079414198342,169.90444625292534</t>
+        </is>
+      </c>
+      <c r="H441" t="inlineStr">
+        <is>
+          <t>-46.308249559402306,169.90367819994196</t>
+        </is>
+      </c>
+      <c r="I441" t="inlineStr">
+        <is>
+          <t>-46.30845822093893,169.9028323198184</t>
+        </is>
+      </c>
+      <c r="J441" t="inlineStr">
+        <is>
+          <t>-46.30879698581776,169.90206931995158</t>
+        </is>
+      </c>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>-46.30915811974601,169.90132071841586</t>
+        </is>
+      </c>
+      <c r="L441" t="inlineStr">
+        <is>
+          <t>-46.309476485284485,169.90054936941146</t>
+        </is>
+      </c>
+      <c r="M441" t="inlineStr">
+        <is>
+          <t>-46.30978013013846,169.89976647329507</t>
+        </is>
+      </c>
+      <c r="N441" t="inlineStr">
+        <is>
+          <t>-46.310077176298044,169.8989776769204</t>
+        </is>
+      </c>
+      <c r="O441" t="inlineStr">
+        <is>
+          <t>-46.31034491126819,169.8981738380314</t>
+        </is>
+      </c>
+      <c r="P441" t="inlineStr">
+        <is>
+          <t>-46.31061179651333,169.89737447947465</t>
+        </is>
+      </c>
+      <c r="Q441" t="inlineStr">
+        <is>
+          <t>-46.31086391665196,169.89655537447345</t>
+        </is>
+      </c>
+      <c r="R441" t="inlineStr">
+        <is>
+          <t>-46.311152172372736,169.8957584803088</t>
+        </is>
+      </c>
+      <c r="S441" t="inlineStr">
+        <is>
+          <t>-46.31147132433905,169.89498173419202</t>
+        </is>
+      </c>
+      <c r="T441" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0527/nzd0527.xlsx
+++ b/data/nzd0527/nzd0527.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T441"/>
+  <dimension ref="A1:T442"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29536,6 +29536,72 @@
       <c r="T441" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:52+00:00</t>
+        </is>
+      </c>
+      <c r="B442" t="n">
+        <v>312.79</v>
+      </c>
+      <c r="C442" t="n">
+        <v>306.08</v>
+      </c>
+      <c r="D442" t="n">
+        <v>304.78</v>
+      </c>
+      <c r="E442" t="n">
+        <v>311.93</v>
+      </c>
+      <c r="F442" t="n">
+        <v>326.93</v>
+      </c>
+      <c r="G442" t="n">
+        <v>329.75</v>
+      </c>
+      <c r="H442" t="n">
+        <v>324.01</v>
+      </c>
+      <c r="I442" t="n">
+        <v>319.82</v>
+      </c>
+      <c r="J442" t="n">
+        <v>326.13</v>
+      </c>
+      <c r="K442" t="n">
+        <v>341.5</v>
+      </c>
+      <c r="L442" t="n">
+        <v>339.07</v>
+      </c>
+      <c r="M442" t="n">
+        <v>334.58</v>
+      </c>
+      <c r="N442" t="n">
+        <v>330.24</v>
+      </c>
+      <c r="O442" t="n">
+        <v>324.42</v>
+      </c>
+      <c r="P442" t="n">
+        <v>327.86</v>
+      </c>
+      <c r="Q442" t="n">
+        <v>324.8</v>
+      </c>
+      <c r="R442" t="n">
+        <v>323.9</v>
+      </c>
+      <c r="S442" t="n">
+        <v>329.92</v>
+      </c>
+      <c r="T442" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -29550,7 +29616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B452"/>
+  <dimension ref="A1:B453"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34073,6 +34139,16 @@
       </c>
       <c r="B452" t="n">
         <v>-0.48</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B453" t="n">
+        <v>-0.29</v>
       </c>
     </row>
   </sheetData>
@@ -34241,28 +34317,28 @@
         <v>0.0503</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7173379518758525</v>
+        <v>0.7097335577715733</v>
       </c>
       <c r="J2" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="K2" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="L2" t="n">
-        <v>0.214352622216014</v>
+        <v>0.2106475891755178</v>
       </c>
       <c r="M2" t="n">
-        <v>7.818410531889221</v>
+        <v>7.839205995606418</v>
       </c>
       <c r="N2" t="n">
-        <v>104.2644529065157</v>
+        <v>104.6503388406787</v>
       </c>
       <c r="O2" t="n">
-        <v>10.21099666567939</v>
+        <v>10.22987482038166</v>
       </c>
       <c r="P2" t="n">
-        <v>310.4862115307633</v>
+        <v>310.5641791151007</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34319,28 +34395,28 @@
         <v>0.0789</v>
       </c>
       <c r="I3" t="n">
-        <v>0.648539989743412</v>
+        <v>0.6381987536954851</v>
       </c>
       <c r="J3" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="K3" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1042300607997428</v>
+        <v>0.1012103546142971</v>
       </c>
       <c r="M3" t="n">
-        <v>10.68457162371297</v>
+        <v>10.72034059535193</v>
       </c>
       <c r="N3" t="n">
-        <v>199.8328125172541</v>
+        <v>200.5305428040265</v>
       </c>
       <c r="O3" t="n">
-        <v>14.13622341777513</v>
+        <v>14.16088072134027</v>
       </c>
       <c r="P3" t="n">
-        <v>311.5730145062462</v>
+        <v>311.6790428344287</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34397,28 +34473,28 @@
         <v>0.075</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7922026393908923</v>
+        <v>0.7794341646695276</v>
       </c>
       <c r="J4" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="K4" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1188224855487793</v>
+        <v>0.1152910126167006</v>
       </c>
       <c r="M4" t="n">
-        <v>11.9661196861725</v>
+        <v>12.01714491789732</v>
       </c>
       <c r="N4" t="n">
-        <v>257.2925024030642</v>
+        <v>258.4635908514346</v>
       </c>
       <c r="O4" t="n">
-        <v>16.04033984686934</v>
+        <v>16.07680288028172</v>
       </c>
       <c r="P4" t="n">
-        <v>311.7898377681635</v>
+        <v>311.9207524887901</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34475,28 +34551,28 @@
         <v>0.0822</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7515982626284892</v>
+        <v>0.7400417413945872</v>
       </c>
       <c r="J5" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="K5" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1541062012268706</v>
+        <v>0.1496978958911377</v>
       </c>
       <c r="M5" t="n">
-        <v>9.364718935458695</v>
+        <v>9.410799616668251</v>
       </c>
       <c r="N5" t="n">
-        <v>171.4182465466692</v>
+        <v>172.4667988355673</v>
       </c>
       <c r="O5" t="n">
-        <v>13.09267912028204</v>
+        <v>13.13266152901107</v>
       </c>
       <c r="P5" t="n">
-        <v>317.3647884181263</v>
+        <v>317.4832770224245</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34553,28 +34629,28 @@
         <v>0.0634</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7786895432117507</v>
+        <v>0.7720042901208826</v>
       </c>
       <c r="J6" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="K6" t="n">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2197905411390033</v>
+        <v>0.2170301699115791</v>
       </c>
       <c r="M6" t="n">
-        <v>7.855271961386316</v>
+        <v>7.870214562952723</v>
       </c>
       <c r="N6" t="n">
-        <v>119.7135007035847</v>
+        <v>119.9251767094265</v>
       </c>
       <c r="O6" t="n">
-        <v>10.94136649160354</v>
+        <v>10.95103541723003</v>
       </c>
       <c r="P6" t="n">
-        <v>321.0071522549195</v>
+        <v>321.0755610717154</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -34631,28 +34707,28 @@
         <v>0.0667</v>
       </c>
       <c r="I7" t="n">
-        <v>1.266111111168453</v>
+        <v>1.258984650012283</v>
       </c>
       <c r="J7" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="K7" t="n">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3519593487442014</v>
+        <v>0.3497906737666189</v>
       </c>
       <c r="M7" t="n">
-        <v>9.650583939986173</v>
+        <v>9.67172368014783</v>
       </c>
       <c r="N7" t="n">
-        <v>164.159347423705</v>
+        <v>164.335677920936</v>
       </c>
       <c r="O7" t="n">
-        <v>12.81246843600814</v>
+        <v>12.81934779623893</v>
       </c>
       <c r="P7" t="n">
-        <v>311.9314999443465</v>
+        <v>312.0044235523249</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -34709,28 +34785,28 @@
         <v>0.06909999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>1.037987124786716</v>
+        <v>1.03072340222837</v>
       </c>
       <c r="J8" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="K8" t="n">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3084755487628239</v>
+        <v>0.3056708676203288</v>
       </c>
       <c r="M8" t="n">
-        <v>8.902711771093436</v>
+        <v>8.924118594944119</v>
       </c>
       <c r="N8" t="n">
-        <v>134.333076392873</v>
+        <v>134.5989380236554</v>
       </c>
       <c r="O8" t="n">
-        <v>11.59021468277758</v>
+        <v>11.60167824168794</v>
       </c>
       <c r="P8" t="n">
-        <v>312.5049339558592</v>
+        <v>312.5792621314714</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -34787,28 +34863,28 @@
         <v>0.0717</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8784250021856113</v>
+        <v>0.8706777696968787</v>
       </c>
       <c r="J9" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="K9" t="n">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2387791985293228</v>
+        <v>0.2356397879663187</v>
       </c>
       <c r="M9" t="n">
-        <v>9.074132887830705</v>
+        <v>9.098997943065708</v>
       </c>
       <c r="N9" t="n">
-        <v>136.8156463805499</v>
+        <v>137.1546016976693</v>
       </c>
       <c r="O9" t="n">
-        <v>11.69682206330206</v>
+        <v>11.71130230579287</v>
       </c>
       <c r="P9" t="n">
-        <v>313.5853904647323</v>
+        <v>313.6646662977925</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -34865,28 +34941,28 @@
         <v>0.0781</v>
       </c>
       <c r="I10" t="n">
-        <v>0.9910044051475331</v>
+        <v>0.9829116094348521</v>
       </c>
       <c r="J10" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="K10" t="n">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="L10" t="n">
-        <v>0.3120658313077951</v>
+        <v>0.3083913898469088</v>
       </c>
       <c r="M10" t="n">
-        <v>7.89906976235139</v>
+        <v>7.927764425419416</v>
       </c>
       <c r="N10" t="n">
-        <v>120.4104178931329</v>
+        <v>120.8462278140193</v>
       </c>
       <c r="O10" t="n">
-        <v>10.9731680882566</v>
+        <v>10.99300813308256</v>
       </c>
       <c r="P10" t="n">
-        <v>317.6847192003654</v>
+        <v>317.7675311106626</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -34943,28 +35019,28 @@
         <v>0.06270000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>1.507781438126072</v>
+        <v>1.497175343939955</v>
       </c>
       <c r="J11" t="n">
+        <v>441</v>
+      </c>
+      <c r="K11" t="n">
         <v>440</v>
       </c>
-      <c r="K11" t="n">
-        <v>439</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.3307964757791969</v>
+        <v>0.3277601216387881</v>
       </c>
       <c r="M11" t="n">
-        <v>11.67918693055288</v>
+        <v>11.71989387162067</v>
       </c>
       <c r="N11" t="n">
-        <v>254.7555138056466</v>
+        <v>255.3904531809342</v>
       </c>
       <c r="O11" t="n">
-        <v>15.96106242722102</v>
+        <v>15.98094030966057</v>
       </c>
       <c r="P11" t="n">
-        <v>324.9045359188217</v>
+        <v>325.0132123303881</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -35021,28 +35097,28 @@
         <v>0.1014</v>
       </c>
       <c r="I12" t="n">
-        <v>1.529630989478639</v>
+        <v>1.51434219458836</v>
       </c>
       <c r="J12" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="K12" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2973008457401042</v>
+        <v>0.2924842047985006</v>
       </c>
       <c r="M12" t="n">
-        <v>12.33204269102901</v>
+        <v>12.40391485511045</v>
       </c>
       <c r="N12" t="n">
-        <v>305.7288484730018</v>
+        <v>307.5510974344659</v>
       </c>
       <c r="O12" t="n">
-        <v>17.48510361630728</v>
+        <v>17.53713481257602</v>
       </c>
       <c r="P12" t="n">
-        <v>332.130115678683</v>
+        <v>332.2868711530413</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -35099,28 +35175,28 @@
         <v>0.0926</v>
       </c>
       <c r="I13" t="n">
-        <v>1.54349169786216</v>
+        <v>1.523476860289961</v>
       </c>
       <c r="J13" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="K13" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2768648643488367</v>
+        <v>0.2702183985865808</v>
       </c>
       <c r="M13" t="n">
-        <v>13.408456696901</v>
+        <v>13.50477901335663</v>
       </c>
       <c r="N13" t="n">
-        <v>343.9933139590079</v>
+        <v>347.524342757593</v>
       </c>
       <c r="O13" t="n">
-        <v>18.54705674653011</v>
+        <v>18.64200479448477</v>
       </c>
       <c r="P13" t="n">
-        <v>337.6037797439382</v>
+        <v>337.8089911670981</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -35177,28 +35253,28 @@
         <v>0.1059</v>
       </c>
       <c r="I14" t="n">
-        <v>1.471764719648093</v>
+        <v>1.450442180102345</v>
       </c>
       <c r="J14" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="K14" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2145796228965378</v>
+        <v>0.2087109158636173</v>
       </c>
       <c r="M14" t="n">
-        <v>15.72696142032074</v>
+        <v>15.82884397679523</v>
       </c>
       <c r="N14" t="n">
-        <v>438.3088604566526</v>
+        <v>442.2077652787886</v>
       </c>
       <c r="O14" t="n">
-        <v>20.93582719781219</v>
+        <v>21.02873665436868</v>
       </c>
       <c r="P14" t="n">
-        <v>338.0173846725251</v>
+        <v>338.2360039178615</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -35255,28 +35331,28 @@
         <v>0.0788</v>
       </c>
       <c r="I15" t="n">
-        <v>1.467729555682154</v>
+        <v>1.446624447695611</v>
       </c>
       <c r="J15" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="K15" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1812294171578087</v>
+        <v>0.1764249481061135</v>
       </c>
       <c r="M15" t="n">
-        <v>17.56791584106881</v>
+        <v>17.66609390559626</v>
       </c>
       <c r="N15" t="n">
-        <v>538.0410401594196</v>
+        <v>541.6145172940356</v>
       </c>
       <c r="O15" t="n">
-        <v>23.19571167607107</v>
+        <v>23.27261303107229</v>
       </c>
       <c r="P15" t="n">
-        <v>331.8262276975557</v>
+        <v>332.0426176247903</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -35333,28 +35409,28 @@
         <v>0.0936</v>
       </c>
       <c r="I16" t="n">
-        <v>1.556592554180257</v>
+        <v>1.536746243985666</v>
       </c>
       <c r="J16" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="K16" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1864531104102213</v>
+        <v>0.182277683725828</v>
       </c>
       <c r="M16" t="n">
-        <v>18.16406131085277</v>
+        <v>18.25837629372722</v>
       </c>
       <c r="N16" t="n">
-        <v>584.4571028502604</v>
+        <v>587.3705686469581</v>
       </c>
       <c r="O16" t="n">
-        <v>24.1755476225516</v>
+        <v>24.23572917506214</v>
       </c>
       <c r="P16" t="n">
-        <v>330.176176251998</v>
+        <v>330.3796597699038</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -35411,28 +35487,28 @@
         <v>0.08169999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>1.93227833474697</v>
+        <v>1.910014839130327</v>
       </c>
       <c r="J17" t="n">
+        <v>441</v>
+      </c>
+      <c r="K17" t="n">
         <v>440</v>
       </c>
-      <c r="K17" t="n">
-        <v>439</v>
-      </c>
       <c r="L17" t="n">
-        <v>0.2613137603802033</v>
+        <v>0.2561088110010199</v>
       </c>
       <c r="M17" t="n">
-        <v>18.11681008026367</v>
+        <v>18.22743346044452</v>
       </c>
       <c r="N17" t="n">
-        <v>581.0616884067582</v>
+        <v>585.0459897087306</v>
       </c>
       <c r="O17" t="n">
-        <v>24.10522118560123</v>
+        <v>24.18772394643057</v>
       </c>
       <c r="P17" t="n">
-        <v>322.2909522596114</v>
+        <v>322.5200290701905</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -35489,28 +35565,28 @@
         <v>0.1195</v>
       </c>
       <c r="I18" t="n">
-        <v>1.986456056883918</v>
+        <v>1.963033268114793</v>
       </c>
       <c r="J18" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="K18" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="L18" t="n">
-        <v>0.3029731315481662</v>
+        <v>0.2966115505175092</v>
       </c>
       <c r="M18" t="n">
-        <v>16.97641535960408</v>
+        <v>17.1022984970587</v>
       </c>
       <c r="N18" t="n">
-        <v>501.8721717898925</v>
+        <v>506.6382848500132</v>
       </c>
       <c r="O18" t="n">
-        <v>22.40250369467423</v>
+        <v>22.50862689836973</v>
       </c>
       <c r="P18" t="n">
-        <v>322.687809937371</v>
+        <v>322.9279629638619</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -35567,28 +35643,28 @@
         <v>0.1194</v>
       </c>
       <c r="I19" t="n">
-        <v>1.871472697254574</v>
+        <v>1.849140353196699</v>
       </c>
       <c r="J19" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="K19" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2985807982989666</v>
+        <v>0.2922061218778438</v>
       </c>
       <c r="M19" t="n">
-        <v>16.12009078285792</v>
+        <v>16.23709718490522</v>
       </c>
       <c r="N19" t="n">
-        <v>454.8545614119664</v>
+        <v>459.1903534126746</v>
       </c>
       <c r="O19" t="n">
-        <v>21.32731960214331</v>
+        <v>21.42872729334793</v>
       </c>
       <c r="P19" t="n">
-        <v>329.3594431989161</v>
+        <v>329.5884159342721</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -35626,7 +35702,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T441"/>
+  <dimension ref="A1:T442"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -80543,6 +80619,108 @@
         </is>
       </c>
     </row>
+    <row r="442">
+      <c r="A442" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:52+00:00</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>-46.306176435098095,169.90814031662998</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>-46.306460759470156,169.90733978871245</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>-46.30678667055393,169.90657569945765</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>-46.30717753878187,169.9058685235657</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>-46.30762875230425,169.90521421928517</t>
+        </is>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>-46.30798469233794,169.90448109900527</t>
+        </is>
+      </c>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>-46.30823216272894,169.90366602016778</t>
+        </is>
+      </c>
+      <c r="I442" t="inlineStr">
+        <is>
+          <t>-46.30847080331861,169.90284067292166</t>
+        </is>
+      </c>
+      <c r="J442" t="inlineStr">
+        <is>
+          <t>-46.30879649559385,169.90206899450888</t>
+        </is>
+      </c>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>-46.309196068813215,169.90134758345354</t>
+        </is>
+      </c>
+      <c r="L442" t="inlineStr">
+        <is>
+          <t>-46.309477743768774,169.9005503762822</t>
+        </is>
+      </c>
+      <c r="M442" t="inlineStr">
+        <is>
+          <t>-46.30977144653518,169.89975910728896</t>
+        </is>
+      </c>
+      <c r="N442" t="inlineStr">
+        <is>
+          <t>-46.310066244220366,169.89896840371048</t>
+        </is>
+      </c>
+      <c r="O442" t="inlineStr">
+        <is>
+          <t>-46.31034642344919,169.89817498634204</t>
+        </is>
+      </c>
+      <c r="P442" t="inlineStr">
+        <is>
+          <t>-46.310648649730695,169.89739892759405</t>
+        </is>
+      </c>
+      <c r="Q442" t="inlineStr">
+        <is>
+          <t>-46.31089366658175,169.8965747749773</t>
+        </is>
+      </c>
+      <c r="R442" t="inlineStr">
+        <is>
+          <t>-46.311156679950535,169.89576141974646</t>
+        </is>
+      </c>
+      <c r="S442" t="inlineStr">
+        <is>
+          <t>-46.31147640562214,169.89498504770825</t>
+        </is>
+      </c>
+      <c r="T442" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0527/nzd0527.xlsx
+++ b/data/nzd0527/nzd0527.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T442"/>
+  <dimension ref="A1:T443"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29602,6 +29602,72 @@
       <c r="T442" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:14:36+00:00</t>
+        </is>
+      </c>
+      <c r="B443" t="n">
+        <v>310.91</v>
+      </c>
+      <c r="C443" t="n">
+        <v>310.85</v>
+      </c>
+      <c r="D443" t="n">
+        <v>309.26</v>
+      </c>
+      <c r="E443" t="n">
+        <v>310.05</v>
+      </c>
+      <c r="F443" t="n">
+        <v>324.51</v>
+      </c>
+      <c r="G443" t="n">
+        <v>324.71</v>
+      </c>
+      <c r="H443" t="n">
+        <v>316.23</v>
+      </c>
+      <c r="I443" t="n">
+        <v>312.01</v>
+      </c>
+      <c r="J443" t="n">
+        <v>321.56</v>
+      </c>
+      <c r="K443" t="n">
+        <v>335.56</v>
+      </c>
+      <c r="L443" t="n">
+        <v>329.74</v>
+      </c>
+      <c r="M443" t="n">
+        <v>331.15</v>
+      </c>
+      <c r="N443" t="n">
+        <v>324.87</v>
+      </c>
+      <c r="O443" t="n">
+        <v>319.72</v>
+      </c>
+      <c r="P443" t="n">
+        <v>321.7</v>
+      </c>
+      <c r="Q443" t="n">
+        <v>320.46</v>
+      </c>
+      <c r="R443" t="n">
+        <v>320.44</v>
+      </c>
+      <c r="S443" t="n">
+        <v>326.71</v>
+      </c>
+      <c r="T443" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -29616,7 +29682,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B453"/>
+  <dimension ref="A1:B454"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34149,6 +34215,16 @@
       </c>
       <c r="B453" t="n">
         <v>-0.29</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B454" t="n">
+        <v>0.35</v>
       </c>
     </row>
   </sheetData>
@@ -34317,28 +34393,28 @@
         <v>0.0503</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7097335577715733</v>
+        <v>0.701198749876748</v>
       </c>
       <c r="J2" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="K2" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2106475891755178</v>
+        <v>0.2063103623486153</v>
       </c>
       <c r="M2" t="n">
-        <v>7.839205995606418</v>
+        <v>7.864294615528081</v>
       </c>
       <c r="N2" t="n">
-        <v>104.6503388406787</v>
+        <v>105.182793675649</v>
       </c>
       <c r="O2" t="n">
-        <v>10.22987482038166</v>
+        <v>10.25586630546874</v>
       </c>
       <c r="P2" t="n">
-        <v>310.5641791151007</v>
+        <v>310.6523491520107</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34395,28 +34471,28 @@
         <v>0.0789</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6381987536954851</v>
+        <v>0.6299968257915509</v>
       </c>
       <c r="J3" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="K3" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1012103546142971</v>
+        <v>0.09903347791915862</v>
       </c>
       <c r="M3" t="n">
-        <v>10.72034059535193</v>
+        <v>10.74314745919322</v>
       </c>
       <c r="N3" t="n">
-        <v>200.5305428040265</v>
+        <v>200.7872410061145</v>
       </c>
       <c r="O3" t="n">
-        <v>14.16088072134027</v>
+        <v>14.16994146092758</v>
       </c>
       <c r="P3" t="n">
-        <v>311.6790428344287</v>
+        <v>311.7637740076356</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34473,28 +34549,28 @@
         <v>0.075</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7794341646695276</v>
+        <v>0.7686561462402742</v>
       </c>
       <c r="J4" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="K4" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1152910126167006</v>
+        <v>0.112531296904779</v>
       </c>
       <c r="M4" t="n">
-        <v>12.01714491789732</v>
+        <v>12.05515294369463</v>
       </c>
       <c r="N4" t="n">
-        <v>258.4635908514346</v>
+        <v>259.1055392762186</v>
       </c>
       <c r="O4" t="n">
-        <v>16.07680288028172</v>
+        <v>16.09675555123512</v>
       </c>
       <c r="P4" t="n">
-        <v>311.9207524887901</v>
+        <v>312.032096328562</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34551,28 +34627,28 @@
         <v>0.0822</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7400417413945872</v>
+        <v>0.7275474671714157</v>
       </c>
       <c r="J5" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="K5" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1496978958911377</v>
+        <v>0.1448832857322442</v>
       </c>
       <c r="M5" t="n">
-        <v>9.410799616668251</v>
+        <v>9.461498237606172</v>
       </c>
       <c r="N5" t="n">
-        <v>172.4667988355673</v>
+        <v>173.7250886271223</v>
       </c>
       <c r="O5" t="n">
-        <v>13.13266152901107</v>
+        <v>13.18048135035752</v>
       </c>
       <c r="P5" t="n">
-        <v>317.4832770224245</v>
+        <v>317.612350884777</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34629,28 +34705,28 @@
         <v>0.0634</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7720042901208826</v>
+        <v>0.7641365590730846</v>
       </c>
       <c r="J6" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="K6" t="n">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2170301699115791</v>
+        <v>0.2135264475568405</v>
       </c>
       <c r="M6" t="n">
-        <v>7.870214562952723</v>
+        <v>7.890641360275256</v>
       </c>
       <c r="N6" t="n">
-        <v>119.9251767094265</v>
+        <v>120.3111095058794</v>
       </c>
       <c r="O6" t="n">
-        <v>10.95103541723003</v>
+        <v>10.96864209945239</v>
       </c>
       <c r="P6" t="n">
-        <v>321.0755610717154</v>
+        <v>321.1566866850802</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -34707,28 +34783,28 @@
         <v>0.0667</v>
       </c>
       <c r="I7" t="n">
-        <v>1.258984650012283</v>
+        <v>1.249423812144838</v>
       </c>
       <c r="J7" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="K7" t="n">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3497906737666189</v>
+        <v>0.3461775066441062</v>
       </c>
       <c r="M7" t="n">
-        <v>9.67172368014783</v>
+        <v>9.707079470070099</v>
       </c>
       <c r="N7" t="n">
-        <v>164.335677920936</v>
+        <v>164.9346473908862</v>
       </c>
       <c r="O7" t="n">
-        <v>12.81934779623893</v>
+        <v>12.84268847986613</v>
       </c>
       <c r="P7" t="n">
-        <v>312.0044235523249</v>
+        <v>312.1030070996737</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -34785,28 +34861,28 @@
         <v>0.06909999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>1.03072340222837</v>
+        <v>1.01978767846597</v>
       </c>
       <c r="J8" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="K8" t="n">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3056708676203288</v>
+        <v>0.3002794646199499</v>
       </c>
       <c r="M8" t="n">
-        <v>8.924118594944119</v>
+        <v>8.966977910807579</v>
       </c>
       <c r="N8" t="n">
-        <v>134.5989380236554</v>
+        <v>135.5657042726613</v>
       </c>
       <c r="O8" t="n">
-        <v>11.60167824168794</v>
+        <v>11.6432686249464</v>
       </c>
       <c r="P8" t="n">
-        <v>312.5792621314714</v>
+        <v>312.6920223786663</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -34863,28 +34939,28 @@
         <v>0.0717</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8706777696968787</v>
+        <v>0.8592550546824337</v>
       </c>
       <c r="J9" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="K9" t="n">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2356397879663187</v>
+        <v>0.230053603547547</v>
       </c>
       <c r="M9" t="n">
-        <v>9.098997943065708</v>
+        <v>9.145096813205406</v>
       </c>
       <c r="N9" t="n">
-        <v>137.1546016976693</v>
+        <v>138.2314834008392</v>
       </c>
       <c r="O9" t="n">
-        <v>11.71130230579287</v>
+        <v>11.75718858404675</v>
       </c>
       <c r="P9" t="n">
-        <v>313.6646662977925</v>
+        <v>313.7824480008284</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -34941,28 +35017,28 @@
         <v>0.0781</v>
       </c>
       <c r="I10" t="n">
-        <v>0.9829116094348521</v>
+        <v>0.9726238194279336</v>
       </c>
       <c r="J10" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="K10" t="n">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="L10" t="n">
-        <v>0.3083913898469088</v>
+        <v>0.3030623444882188</v>
       </c>
       <c r="M10" t="n">
-        <v>7.927764425419416</v>
+        <v>7.969234603215559</v>
       </c>
       <c r="N10" t="n">
-        <v>120.8462278140193</v>
+        <v>121.697899075391</v>
       </c>
       <c r="O10" t="n">
-        <v>10.99300813308256</v>
+        <v>11.03167707447018</v>
       </c>
       <c r="P10" t="n">
-        <v>317.7675311106626</v>
+        <v>317.873610394437</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -35019,28 +35095,28 @@
         <v>0.06270000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>1.497175343939955</v>
+        <v>1.483697693578595</v>
       </c>
       <c r="J11" t="n">
+        <v>442</v>
+      </c>
+      <c r="K11" t="n">
         <v>441</v>
       </c>
-      <c r="K11" t="n">
-        <v>440</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.3277601216387881</v>
+        <v>0.3232904087814452</v>
       </c>
       <c r="M11" t="n">
-        <v>11.71989387162067</v>
+        <v>11.77951527505986</v>
       </c>
       <c r="N11" t="n">
-        <v>255.3904531809342</v>
+        <v>256.7348062896116</v>
       </c>
       <c r="O11" t="n">
-        <v>15.98094030966057</v>
+        <v>16.02294624248648</v>
       </c>
       <c r="P11" t="n">
-        <v>325.0132123303881</v>
+        <v>325.152362536031</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -35097,28 +35173,28 @@
         <v>0.1014</v>
       </c>
       <c r="I12" t="n">
-        <v>1.51434219458836</v>
+        <v>1.494614881703151</v>
       </c>
       <c r="J12" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="K12" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2924842047985006</v>
+        <v>0.2854418325761852</v>
       </c>
       <c r="M12" t="n">
-        <v>12.40391485511045</v>
+        <v>12.5038124831651</v>
       </c>
       <c r="N12" t="n">
-        <v>307.5510974344659</v>
+        <v>310.9648762457625</v>
       </c>
       <c r="O12" t="n">
-        <v>17.53713481257602</v>
+        <v>17.63419621774019</v>
       </c>
       <c r="P12" t="n">
-        <v>332.2868711530413</v>
+        <v>332.4906669416119</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -35175,28 +35251,28 @@
         <v>0.0926</v>
       </c>
       <c r="I13" t="n">
-        <v>1.523476860289961</v>
+        <v>1.501738627979963</v>
       </c>
       <c r="J13" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="K13" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2702183985865808</v>
+        <v>0.2628331132384902</v>
       </c>
       <c r="M13" t="n">
-        <v>13.50477901335663</v>
+        <v>13.61223249086395</v>
       </c>
       <c r="N13" t="n">
-        <v>347.524342757593</v>
+        <v>351.7282166586823</v>
       </c>
       <c r="O13" t="n">
-        <v>18.64200479448477</v>
+        <v>18.7544185902598</v>
       </c>
       <c r="P13" t="n">
-        <v>337.8089911670981</v>
+        <v>338.0335610424545</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -35253,28 +35329,28 @@
         <v>0.1059</v>
       </c>
       <c r="I14" t="n">
-        <v>1.450442180102345</v>
+        <v>1.426506000727689</v>
       </c>
       <c r="J14" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="K14" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2087109158636173</v>
+        <v>0.2019160639952177</v>
       </c>
       <c r="M14" t="n">
-        <v>15.82884397679523</v>
+        <v>15.94543345970627</v>
       </c>
       <c r="N14" t="n">
-        <v>442.2077652787886</v>
+        <v>447.2575393945498</v>
       </c>
       <c r="O14" t="n">
-        <v>21.02873665436868</v>
+        <v>21.1484642325288</v>
       </c>
       <c r="P14" t="n">
-        <v>338.2360039178615</v>
+        <v>338.4832799954202</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -35331,28 +35407,28 @@
         <v>0.0788</v>
       </c>
       <c r="I15" t="n">
-        <v>1.446624447695611</v>
+        <v>1.423216184134192</v>
       </c>
       <c r="J15" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="K15" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1764249481061135</v>
+        <v>0.1709676079350895</v>
       </c>
       <c r="M15" t="n">
-        <v>17.66609390559626</v>
+        <v>17.77736556420789</v>
       </c>
       <c r="N15" t="n">
-        <v>541.6145172940356</v>
+        <v>546.1754542939292</v>
       </c>
       <c r="O15" t="n">
-        <v>23.27261303107229</v>
+        <v>23.37039696483415</v>
       </c>
       <c r="P15" t="n">
-        <v>332.0426176247903</v>
+        <v>332.2844399935705</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -35409,28 +35485,28 @@
         <v>0.0936</v>
       </c>
       <c r="I16" t="n">
-        <v>1.536746243985666</v>
+        <v>1.513916399006562</v>
       </c>
       <c r="J16" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="K16" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="L16" t="n">
-        <v>0.182277683725828</v>
+        <v>0.1772600748915949</v>
       </c>
       <c r="M16" t="n">
-        <v>18.25837629372722</v>
+        <v>18.37102663546045</v>
       </c>
       <c r="N16" t="n">
-        <v>587.3705686469581</v>
+        <v>591.5455586079675</v>
       </c>
       <c r="O16" t="n">
-        <v>24.23572917506214</v>
+        <v>24.32170961523814</v>
       </c>
       <c r="P16" t="n">
-        <v>330.3796597699038</v>
+        <v>330.6155067039255</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -35487,28 +35563,28 @@
         <v>0.08169999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>1.910014839130327</v>
+        <v>1.885568644471527</v>
       </c>
       <c r="J17" t="n">
+        <v>442</v>
+      </c>
+      <c r="K17" t="n">
         <v>441</v>
       </c>
-      <c r="K17" t="n">
-        <v>440</v>
-      </c>
       <c r="L17" t="n">
-        <v>0.2561088110010199</v>
+        <v>0.2502104692822659</v>
       </c>
       <c r="M17" t="n">
-        <v>18.22743346044452</v>
+        <v>18.35047540166129</v>
       </c>
       <c r="N17" t="n">
-        <v>585.0459897087306</v>
+        <v>589.9951667699955</v>
       </c>
       <c r="O17" t="n">
-        <v>24.18772394643057</v>
+        <v>24.28981611231331</v>
       </c>
       <c r="P17" t="n">
-        <v>322.5200290701905</v>
+        <v>322.7734650154661</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -35565,28 +35641,28 @@
         <v>0.1195</v>
       </c>
       <c r="I18" t="n">
-        <v>1.963033268114793</v>
+        <v>1.937834770434501</v>
       </c>
       <c r="J18" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="K18" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2966115505175092</v>
+        <v>0.289615823424868</v>
       </c>
       <c r="M18" t="n">
-        <v>17.1022984970587</v>
+        <v>17.23830470467304</v>
       </c>
       <c r="N18" t="n">
-        <v>506.6382848500132</v>
+        <v>512.1972567777276</v>
       </c>
       <c r="O18" t="n">
-        <v>22.50862689836973</v>
+        <v>22.63177537838619</v>
       </c>
       <c r="P18" t="n">
-        <v>322.9279629638619</v>
+        <v>323.1882795987443</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -35643,28 +35719,28 @@
         <v>0.1194</v>
       </c>
       <c r="I19" t="n">
-        <v>1.849140353196699</v>
+        <v>1.82515383755031</v>
       </c>
       <c r="J19" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="K19" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2922061218778438</v>
+        <v>0.2852169826245438</v>
       </c>
       <c r="M19" t="n">
-        <v>16.23709718490522</v>
+        <v>16.36324271457316</v>
       </c>
       <c r="N19" t="n">
-        <v>459.1903534126746</v>
+        <v>464.2271787014656</v>
       </c>
       <c r="O19" t="n">
-        <v>21.42872729334793</v>
+        <v>21.54593183646197</v>
       </c>
       <c r="P19" t="n">
-        <v>329.5884159342721</v>
+        <v>329.8362120177866</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -35702,7 +35778,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T442"/>
+  <dimension ref="A1:T443"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -80721,6 +80797,108 @@
         </is>
       </c>
     </row>
+    <row r="443">
+      <c r="A443" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:14:36+00:00</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>-46.30616198278261,169.90812765405354</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>-46.3064974285186,169.90737191643157</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>-46.306821110377086,169.9066058737467</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>-46.30716308630525,169.90585586119434</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>-46.30761014852828,169.90519791987035</t>
+        </is>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>-46.307945110955586,169.90444922527487</t>
+        </is>
+      </c>
+      <c r="H443" t="inlineStr">
+        <is>
+          <t>-46.308169211036095,169.903621946443</t>
+        </is>
+      </c>
+      <c r="I443" t="inlineStr">
+        <is>
+          <t>-46.30840699267326,169.90279831079357</t>
+        </is>
+      </c>
+      <c r="J443" t="inlineStr">
+        <is>
+          <t>-46.30875915687108,169.90204420663937</t>
+        </is>
+      </c>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>-46.309148107650735,169.90131363062468</t>
+        </is>
+      </c>
+      <c r="L443" t="inlineStr">
+        <is>
+          <t>-46.3094043583903,169.90049166320642</t>
+        </is>
+      </c>
+      <c r="M443" t="inlineStr">
+        <is>
+          <t>-46.30974485299747,169.8997365489094</t>
+        </is>
+      </c>
+      <c r="N443" t="inlineStr">
+        <is>
+          <t>-46.310024609280035,169.89893308662508</t>
+        </is>
+      </c>
+      <c r="O443" t="inlineStr">
+        <is>
+          <t>-46.31030901686334,169.89814658078103</t>
+        </is>
+      </c>
+      <c r="P443" t="inlineStr">
+        <is>
+          <t>-46.310598313627764,169.89736553504866</t>
+        </is>
+      </c>
+      <c r="Q443" t="inlineStr">
+        <is>
+          <t>-46.310858097794835,169.89655157988693</t>
+        </is>
+      </c>
+      <c r="R443" t="inlineStr">
+        <is>
+          <t>-46.31112832318726,169.89574292801922</t>
+        </is>
+      </c>
+      <c r="S443" t="inlineStr">
+        <is>
+          <t>-46.31145009768784,169.89496789225154</t>
+        </is>
+      </c>
+      <c r="T443" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0527/nzd0527.xlsx
+++ b/data/nzd0527/nzd0527.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T443"/>
+  <dimension ref="A1:T445"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29668,6 +29668,138 @@
       <c r="T443" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:14:31+00:00</t>
+        </is>
+      </c>
+      <c r="B444" t="n">
+        <v>308.1</v>
+      </c>
+      <c r="C444" t="n">
+        <v>307.24</v>
+      </c>
+      <c r="D444" t="n">
+        <v>305.31</v>
+      </c>
+      <c r="E444" t="n">
+        <v>307.99</v>
+      </c>
+      <c r="F444" t="n">
+        <v>323.01</v>
+      </c>
+      <c r="G444" t="n">
+        <v>319</v>
+      </c>
+      <c r="H444" t="n">
+        <v>312.24</v>
+      </c>
+      <c r="I444" t="n">
+        <v>308.26</v>
+      </c>
+      <c r="J444" t="n">
+        <v>321.25</v>
+      </c>
+      <c r="K444" t="n">
+        <v>334.87</v>
+      </c>
+      <c r="L444" t="n">
+        <v>329.51</v>
+      </c>
+      <c r="M444" t="n">
+        <v>329.56</v>
+      </c>
+      <c r="N444" t="n">
+        <v>322.55</v>
+      </c>
+      <c r="O444" t="n">
+        <v>318.5</v>
+      </c>
+      <c r="P444" t="n">
+        <v>318.88</v>
+      </c>
+      <c r="Q444" t="n">
+        <v>319.47</v>
+      </c>
+      <c r="R444" t="n">
+        <v>322.91</v>
+      </c>
+      <c r="S444" t="n">
+        <v>332.14</v>
+      </c>
+      <c r="T444" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:20:21+00:00</t>
+        </is>
+      </c>
+      <c r="B445" t="n">
+        <v>306.15</v>
+      </c>
+      <c r="C445" t="n">
+        <v>303.79</v>
+      </c>
+      <c r="D445" t="n">
+        <v>300.88</v>
+      </c>
+      <c r="E445" t="n">
+        <v>308.2</v>
+      </c>
+      <c r="F445" t="n">
+        <v>323.91</v>
+      </c>
+      <c r="G445" t="n">
+        <v>316.28</v>
+      </c>
+      <c r="H445" t="n">
+        <v>311.95</v>
+      </c>
+      <c r="I445" t="n">
+        <v>307.82</v>
+      </c>
+      <c r="J445" t="n">
+        <v>321.57</v>
+      </c>
+      <c r="K445" t="n">
+        <v>334.14</v>
+      </c>
+      <c r="L445" t="n">
+        <v>331.22</v>
+      </c>
+      <c r="M445" t="n">
+        <v>330.48</v>
+      </c>
+      <c r="N445" t="n">
+        <v>323.41</v>
+      </c>
+      <c r="O445" t="n">
+        <v>316.73</v>
+      </c>
+      <c r="P445" t="n">
+        <v>317.16</v>
+      </c>
+      <c r="Q445" t="n">
+        <v>321.16</v>
+      </c>
+      <c r="R445" t="n">
+        <v>326.36</v>
+      </c>
+      <c r="S445" t="n">
+        <v>336.92</v>
+      </c>
+      <c r="T445" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -29682,7 +29814,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B454"/>
+  <dimension ref="A1:B456"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34225,6 +34357,26 @@
       </c>
       <c r="B454" t="n">
         <v>0.35</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B455" t="n">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B456" t="n">
+        <v>0.38</v>
       </c>
     </row>
   </sheetData>
@@ -34393,28 +34545,28 @@
         <v>0.0503</v>
       </c>
       <c r="I2" t="n">
-        <v>0.701198749876748</v>
+        <v>0.6809102160188234</v>
       </c>
       <c r="J2" t="n">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="K2" t="n">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2063103623486153</v>
+        <v>0.1952452592614182</v>
       </c>
       <c r="M2" t="n">
-        <v>7.864294615528081</v>
+        <v>7.93175929435571</v>
       </c>
       <c r="N2" t="n">
-        <v>105.182793675649</v>
+        <v>106.9009502404258</v>
       </c>
       <c r="O2" t="n">
-        <v>10.25586630546874</v>
+        <v>10.33929157343122</v>
       </c>
       <c r="P2" t="n">
-        <v>310.6523491520107</v>
+        <v>310.8625126454931</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34471,28 +34623,28 @@
         <v>0.0789</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6299968257915509</v>
+        <v>0.6089505552492562</v>
       </c>
       <c r="J3" t="n">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="K3" t="n">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="L3" t="n">
-        <v>0.09903347791915862</v>
+        <v>0.09302301001962465</v>
       </c>
       <c r="M3" t="n">
-        <v>10.74314745919322</v>
+        <v>10.81497580019948</v>
       </c>
       <c r="N3" t="n">
-        <v>200.7872410061145</v>
+        <v>202.2501077845839</v>
       </c>
       <c r="O3" t="n">
-        <v>14.16994146092758</v>
+        <v>14.22146644283155</v>
       </c>
       <c r="P3" t="n">
-        <v>311.7637740076356</v>
+        <v>311.9817924853615</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34549,28 +34701,28 @@
         <v>0.075</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7686561462402742</v>
+        <v>0.74177730017427</v>
       </c>
       <c r="J4" t="n">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="K4" t="n">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="L4" t="n">
-        <v>0.112531296904779</v>
+        <v>0.1052014334736161</v>
       </c>
       <c r="M4" t="n">
-        <v>12.05515294369463</v>
+        <v>12.16284574218616</v>
       </c>
       <c r="N4" t="n">
-        <v>259.1055392762186</v>
+        <v>261.7999258525973</v>
       </c>
       <c r="O4" t="n">
-        <v>16.09675555123512</v>
+        <v>16.18023256484891</v>
       </c>
       <c r="P4" t="n">
-        <v>312.032096328562</v>
+        <v>312.3105346211659</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34627,28 +34779,28 @@
         <v>0.0822</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7275474671714157</v>
+        <v>0.7011472966554018</v>
       </c>
       <c r="J5" t="n">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="K5" t="n">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1448832857322442</v>
+        <v>0.1347079559701457</v>
       </c>
       <c r="M5" t="n">
-        <v>9.461498237606172</v>
+        <v>9.574069125641671</v>
       </c>
       <c r="N5" t="n">
-        <v>173.7250886271223</v>
+        <v>176.6472217210499</v>
       </c>
       <c r="O5" t="n">
-        <v>13.18048135035752</v>
+        <v>13.29086986322001</v>
       </c>
       <c r="P5" t="n">
-        <v>317.612350884777</v>
+        <v>317.885811968896</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34705,28 +34857,28 @@
         <v>0.0634</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7641365590730846</v>
+        <v>0.7476583004857625</v>
       </c>
       <c r="J6" t="n">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="K6" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2135264475568405</v>
+        <v>0.2060274118644486</v>
       </c>
       <c r="M6" t="n">
-        <v>7.890641360275256</v>
+        <v>7.935792077875973</v>
       </c>
       <c r="N6" t="n">
-        <v>120.3111095058794</v>
+        <v>121.2217020932262</v>
       </c>
       <c r="O6" t="n">
-        <v>10.96864209945239</v>
+        <v>11.01007275603691</v>
       </c>
       <c r="P6" t="n">
-        <v>321.1566866850802</v>
+        <v>321.3270539532163</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -34783,28 +34935,28 @@
         <v>0.0667</v>
       </c>
       <c r="I7" t="n">
-        <v>1.249423812144838</v>
+        <v>1.224089732260248</v>
       </c>
       <c r="J7" t="n">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="K7" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3461775066441062</v>
+        <v>0.3346583496146439</v>
       </c>
       <c r="M7" t="n">
-        <v>9.707079470070099</v>
+        <v>9.816441735082359</v>
       </c>
       <c r="N7" t="n">
-        <v>164.9346473908862</v>
+        <v>167.6343882146306</v>
       </c>
       <c r="O7" t="n">
-        <v>12.84268847986613</v>
+        <v>12.94736993426196</v>
       </c>
       <c r="P7" t="n">
-        <v>312.1030070996737</v>
+        <v>312.3649508348216</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -34861,28 +35013,28 @@
         <v>0.06909999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>1.01978767846597</v>
+        <v>0.9944413532457116</v>
       </c>
       <c r="J8" t="n">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="K8" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3002794646199499</v>
+        <v>0.2867844541134295</v>
       </c>
       <c r="M8" t="n">
-        <v>8.966977910807579</v>
+        <v>9.073579609657594</v>
       </c>
       <c r="N8" t="n">
-        <v>135.5657042726613</v>
+        <v>138.3939498683131</v>
       </c>
       <c r="O8" t="n">
-        <v>11.6432686249464</v>
+        <v>11.76409579476099</v>
       </c>
       <c r="P8" t="n">
-        <v>312.6920223786663</v>
+        <v>312.954082726717</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -34939,28 +35091,28 @@
         <v>0.0717</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8592550546824337</v>
+        <v>0.8331182862586025</v>
       </c>
       <c r="J9" t="n">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="K9" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="L9" t="n">
-        <v>0.230053603547547</v>
+        <v>0.2165980080529305</v>
       </c>
       <c r="M9" t="n">
-        <v>9.145096813205406</v>
+        <v>9.258971689426978</v>
       </c>
       <c r="N9" t="n">
-        <v>138.2314834008392</v>
+        <v>141.2658232290358</v>
       </c>
       <c r="O9" t="n">
-        <v>11.75718858404675</v>
+        <v>11.88552999361138</v>
       </c>
       <c r="P9" t="n">
-        <v>313.7824480008284</v>
+        <v>314.0526814006905</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -35017,28 +35169,28 @@
         <v>0.0781</v>
       </c>
       <c r="I10" t="n">
-        <v>0.9726238194279336</v>
+        <v>0.9521989175923576</v>
       </c>
       <c r="J10" t="n">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="K10" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="L10" t="n">
-        <v>0.3030623444882188</v>
+        <v>0.2925467357922797</v>
       </c>
       <c r="M10" t="n">
-        <v>7.969234603215559</v>
+        <v>8.053719085362493</v>
       </c>
       <c r="N10" t="n">
-        <v>121.697899075391</v>
+        <v>123.381891124418</v>
       </c>
       <c r="O10" t="n">
-        <v>11.03167707447018</v>
+        <v>11.10774014480074</v>
       </c>
       <c r="P10" t="n">
-        <v>317.873610394437</v>
+        <v>318.0847849732875</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -35095,28 +35247,28 @@
         <v>0.06270000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>1.483697693578595</v>
+        <v>1.456140950793207</v>
       </c>
       <c r="J11" t="n">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="K11" t="n">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3232904087814452</v>
+        <v>0.3140097100463096</v>
       </c>
       <c r="M11" t="n">
-        <v>11.77951527505986</v>
+        <v>11.9040576235529</v>
       </c>
       <c r="N11" t="n">
-        <v>256.7348062896116</v>
+        <v>259.623589486754</v>
       </c>
       <c r="O11" t="n">
-        <v>16.02294624248648</v>
+        <v>16.11283927452744</v>
       </c>
       <c r="P11" t="n">
-        <v>325.152362536031</v>
+        <v>325.4376412398141</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -35173,28 +35325,28 @@
         <v>0.1014</v>
       </c>
       <c r="I12" t="n">
-        <v>1.494614881703151</v>
+        <v>1.456298204088905</v>
       </c>
       <c r="J12" t="n">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="K12" t="n">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2854418325761852</v>
+        <v>0.2720975777344823</v>
       </c>
       <c r="M12" t="n">
-        <v>12.5038124831651</v>
+        <v>12.69572154303407</v>
       </c>
       <c r="N12" t="n">
-        <v>310.9648762457625</v>
+        <v>317.3715084635406</v>
       </c>
       <c r="O12" t="n">
-        <v>17.63419621774019</v>
+        <v>17.81492375688261</v>
       </c>
       <c r="P12" t="n">
-        <v>332.4906669416119</v>
+        <v>332.88755721662</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -35251,28 +35403,28 @@
         <v>0.0926</v>
       </c>
       <c r="I13" t="n">
-        <v>1.501738627979963</v>
+        <v>1.457870877914265</v>
       </c>
       <c r="J13" t="n">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="K13" t="n">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2628331132384902</v>
+        <v>0.2480730198352556</v>
       </c>
       <c r="M13" t="n">
-        <v>13.61223249086395</v>
+        <v>13.8328761055941</v>
       </c>
       <c r="N13" t="n">
-        <v>351.7282166586823</v>
+        <v>360.3736888650506</v>
       </c>
       <c r="O13" t="n">
-        <v>18.7544185902598</v>
+        <v>18.98351097308005</v>
       </c>
       <c r="P13" t="n">
-        <v>338.0335610424545</v>
+        <v>338.4879543838056</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -35329,28 +35481,28 @@
         <v>0.1059</v>
       </c>
       <c r="I14" t="n">
-        <v>1.426506000727689</v>
+        <v>1.377623897736714</v>
       </c>
       <c r="J14" t="n">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="K14" t="n">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2019160639952177</v>
+        <v>0.1881988019892324</v>
       </c>
       <c r="M14" t="n">
-        <v>15.94543345970627</v>
+        <v>16.18236290981415</v>
       </c>
       <c r="N14" t="n">
-        <v>447.2575393945498</v>
+        <v>457.9446486323906</v>
       </c>
       <c r="O14" t="n">
-        <v>21.1484642325288</v>
+        <v>21.39964132018083</v>
       </c>
       <c r="P14" t="n">
-        <v>338.4832799954202</v>
+        <v>338.9896139176514</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -35407,28 +35559,28 @@
         <v>0.0788</v>
       </c>
       <c r="I15" t="n">
-        <v>1.423216184134192</v>
+        <v>1.375174755870432</v>
       </c>
       <c r="J15" t="n">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="K15" t="n">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1709676079350895</v>
+        <v>0.1598546625431109</v>
       </c>
       <c r="M15" t="n">
-        <v>17.77736556420789</v>
+        <v>18.00890656864478</v>
       </c>
       <c r="N15" t="n">
-        <v>546.1754542939292</v>
+        <v>555.9858201540305</v>
       </c>
       <c r="O15" t="n">
-        <v>23.37039696483415</v>
+        <v>23.57935156347669</v>
       </c>
       <c r="P15" t="n">
-        <v>332.2844399935705</v>
+        <v>332.7820767008999</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -35485,28 +35637,28 @@
         <v>0.0936</v>
       </c>
       <c r="I16" t="n">
-        <v>1.513916399006562</v>
+        <v>1.465560804428758</v>
       </c>
       <c r="J16" t="n">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="K16" t="n">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1772600748915949</v>
+        <v>0.1665376312131469</v>
       </c>
       <c r="M16" t="n">
-        <v>18.37102663546045</v>
+        <v>18.61315063455025</v>
       </c>
       <c r="N16" t="n">
-        <v>591.5455586079675</v>
+        <v>601.312338266652</v>
       </c>
       <c r="O16" t="n">
-        <v>24.32170961523814</v>
+        <v>24.52167078864432</v>
       </c>
       <c r="P16" t="n">
-        <v>330.6155067039255</v>
+        <v>331.1163974463663</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -35563,28 +35715,28 @@
         <v>0.08169999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>1.885568644471527</v>
+        <v>1.837245401509773</v>
       </c>
       <c r="J17" t="n">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="K17" t="n">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2502104692822659</v>
+        <v>0.2387156289473722</v>
       </c>
       <c r="M17" t="n">
-        <v>18.35047540166129</v>
+        <v>18.59334270469257</v>
       </c>
       <c r="N17" t="n">
-        <v>589.9951667699955</v>
+        <v>599.6782429123623</v>
       </c>
       <c r="O17" t="n">
-        <v>24.28981611231331</v>
+        <v>24.48832870802665</v>
       </c>
       <c r="P17" t="n">
-        <v>322.7734650154661</v>
+        <v>323.2757693257729</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -35641,28 +35793,28 @@
         <v>0.1195</v>
       </c>
       <c r="I18" t="n">
-        <v>1.937834770434501</v>
+        <v>1.891998949408415</v>
       </c>
       <c r="J18" t="n">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="K18" t="n">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="L18" t="n">
-        <v>0.289615823424868</v>
+        <v>0.27761003049898</v>
       </c>
       <c r="M18" t="n">
-        <v>17.23830470467304</v>
+        <v>17.47988331873368</v>
       </c>
       <c r="N18" t="n">
-        <v>512.1972567777276</v>
+        <v>521.0713010785098</v>
       </c>
       <c r="O18" t="n">
-        <v>22.63177537838619</v>
+        <v>22.82698624607528</v>
       </c>
       <c r="P18" t="n">
-        <v>323.1882795987443</v>
+        <v>323.6630486443581</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -35719,28 +35871,28 @@
         <v>0.1194</v>
       </c>
       <c r="I19" t="n">
-        <v>1.82515383755031</v>
+        <v>1.785025969520006</v>
       </c>
       <c r="J19" t="n">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="K19" t="n">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2852169826245438</v>
+        <v>0.2746554224775748</v>
       </c>
       <c r="M19" t="n">
-        <v>16.36324271457316</v>
+        <v>16.55991360834801</v>
       </c>
       <c r="N19" t="n">
-        <v>464.2271787014656</v>
+        <v>470.7215574431442</v>
       </c>
       <c r="O19" t="n">
-        <v>21.54593183646197</v>
+        <v>21.6961184879495</v>
       </c>
       <c r="P19" t="n">
-        <v>329.8362120177866</v>
+        <v>330.2518507734918</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -35778,7 +35930,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T443"/>
+  <dimension ref="A1:T445"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -80899,6 +81051,210 @@
         </is>
       </c>
     </row>
+    <row r="444">
+      <c r="A444" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:14:31+00:00</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>-46.306140381181024,169.9081087275553</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>-46.30646967689149,169.9073476017388</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>-46.306790744908376,169.90657926918186</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>-46.30714725007942,169.90584198647582</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>-46.30759861726113,169.90518781693274</t>
+        </is>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>-46.30790026775281,169.90441311441646</t>
+        </is>
+      </c>
+      <c r="H444" t="inlineStr">
+        <is>
+          <t>-46.30813692603611,169.90359934311843</t>
+        </is>
+      </c>
+      <c r="I444" t="inlineStr">
+        <is>
+          <t>-46.30837635375411,169.90277797049717</t>
+        </is>
+      </c>
+      <c r="J444" t="inlineStr">
+        <is>
+          <t>-46.30875662404727,169.9020425251877</t>
+        </is>
+      </c>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>-46.30914253640401,169.90130968661296</t>
+        </is>
+      </c>
+      <c r="L444" t="inlineStr">
+        <is>
+          <t>-46.30940254931848,169.90049021583354</t>
+        </is>
+      </c>
+      <c r="M444" t="inlineStr">
+        <is>
+          <t>-46.30973252537949,169.8997260918253</t>
+        </is>
+      </c>
+      <c r="N444" t="inlineStr">
+        <is>
+          <t>-46.31000662174224,169.89891782860818</t>
+        </is>
+      </c>
+      <c r="O444" t="inlineStr">
+        <is>
+          <t>-46.31029930706767,169.8981392074288</t>
+        </is>
+      </c>
+      <c r="P444" t="inlineStr">
+        <is>
+          <t>-46.31057527014919,169.8973502482214</t>
+        </is>
+      </c>
+      <c r="Q444" t="inlineStr">
+        <is>
+          <t>-46.31084998417697,169.89654628884506</t>
+        </is>
+      </c>
+      <c r="R444" t="inlineStr">
+        <is>
+          <t>-46.31114856631044,169.89575612875902</t>
+        </is>
+      </c>
+      <c r="S444" t="inlineStr">
+        <is>
+          <t>-46.311494599893116,169.89499691223904</t>
+        </is>
+      </c>
+      <c r="T444" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:20:21+00:00</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>-46.30612539074408,169.90809559351703</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>-46.30644315524901,169.90732436472808</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>-46.306756689452,169.90654943169164</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>-46.307148864452024,169.9058434008885</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>-46.30760553602152,169.9051938786948</t>
+        </is>
+      </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>-46.30787890636365,169.90439591276686</t>
+        </is>
+      </c>
+      <c r="H445" t="inlineStr">
+        <is>
+          <t>-46.30813457950714,169.90359770027132</t>
+        </is>
+      </c>
+      <c r="I445" t="inlineStr">
+        <is>
+          <t>-46.308372758787385,169.9027755839038</t>
+        </is>
+      </c>
+      <c r="J445" t="inlineStr">
+        <is>
+          <t>-46.30875923857508,169.90204426087976</t>
+        </is>
+      </c>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>-46.30913664218633,169.9013055139637</t>
+        </is>
+      </c>
+      <c r="L445" t="inlineStr">
+        <is>
+          <t>-46.30941599937391,169.90050097673875</t>
+        </is>
+      </c>
+      <c r="M445" t="inlineStr">
+        <is>
+          <t>-46.30973965834094,169.8997321424646</t>
+        </is>
+      </c>
+      <c r="N445" t="inlineStr">
+        <is>
+          <t>-46.31001328953663,169.89892348459605</t>
+        </is>
+      </c>
+      <c r="O445" t="inlineStr">
+        <is>
+          <t>-46.31028521990437,169.8981285100289</t>
+        </is>
+      </c>
+      <c r="P445" t="inlineStr">
+        <is>
+          <t>-46.310561215260655,169.89734092434708</t>
+        </is>
+      </c>
+      <c r="Q445" t="inlineStr">
+        <is>
+          <t>-46.31086383469623,169.8965553210286</t>
+        </is>
+      </c>
+      <c r="R445" t="inlineStr">
+        <is>
+          <t>-46.31117684111587,169.89577456705513</t>
+        </is>
+      </c>
+      <c r="S445" t="inlineStr">
+        <is>
+          <t>-46.311533774941395,169.89502245841678</t>
+        </is>
+      </c>
+      <c r="T445" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0527/nzd0527.xlsx
+++ b/data/nzd0527/nzd0527.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T445"/>
+  <dimension ref="A1:T450"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29798,6 +29798,336 @@
         <v>336.92</v>
       </c>
       <c r="T445" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:14:08+00:00</t>
+        </is>
+      </c>
+      <c r="B446" t="n">
+        <v>306</v>
+      </c>
+      <c r="C446" t="n">
+        <v>303.41</v>
+      </c>
+      <c r="D446" t="n">
+        <v>301.48</v>
+      </c>
+      <c r="E446" t="n">
+        <v>309.48</v>
+      </c>
+      <c r="F446" t="n">
+        <v>324.04</v>
+      </c>
+      <c r="G446" t="n">
+        <v>316.87</v>
+      </c>
+      <c r="H446" t="n">
+        <v>313.2</v>
+      </c>
+      <c r="I446" t="n">
+        <v>309.71</v>
+      </c>
+      <c r="J446" t="n">
+        <v>321.6</v>
+      </c>
+      <c r="K446" t="n">
+        <v>333.98</v>
+      </c>
+      <c r="L446" t="n">
+        <v>331.75</v>
+      </c>
+      <c r="M446" t="n">
+        <v>330.76</v>
+      </c>
+      <c r="N446" t="n">
+        <v>324.09</v>
+      </c>
+      <c r="O446" t="n">
+        <v>317.47</v>
+      </c>
+      <c r="P446" t="n">
+        <v>317.71</v>
+      </c>
+      <c r="Q446" t="n">
+        <v>321.85</v>
+      </c>
+      <c r="R446" t="n">
+        <v>327.65</v>
+      </c>
+      <c r="S446" t="n">
+        <v>338.32</v>
+      </c>
+      <c r="T446" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:17+00:00</t>
+        </is>
+      </c>
+      <c r="B447" t="n">
+        <v>304.59</v>
+      </c>
+      <c r="C447" t="n">
+        <v>302.31</v>
+      </c>
+      <c r="D447" t="n">
+        <v>301.18</v>
+      </c>
+      <c r="E447" t="n">
+        <v>309.37</v>
+      </c>
+      <c r="F447" t="n">
+        <v>323.35</v>
+      </c>
+      <c r="G447" t="n">
+        <v>316.32</v>
+      </c>
+      <c r="H447" t="n">
+        <v>313.45</v>
+      </c>
+      <c r="I447" t="n">
+        <v>309.49</v>
+      </c>
+      <c r="J447" t="n">
+        <v>320.94</v>
+      </c>
+      <c r="K447" t="n">
+        <v>333.13</v>
+      </c>
+      <c r="L447" t="n">
+        <v>331.63</v>
+      </c>
+      <c r="M447" t="n">
+        <v>330.72</v>
+      </c>
+      <c r="N447" t="n">
+        <v>325.22</v>
+      </c>
+      <c r="O447" t="n">
+        <v>317.96</v>
+      </c>
+      <c r="P447" t="n">
+        <v>319.7</v>
+      </c>
+      <c r="Q447" t="n">
+        <v>322.87</v>
+      </c>
+      <c r="R447" t="n">
+        <v>327.16</v>
+      </c>
+      <c r="S447" t="n">
+        <v>337.19</v>
+      </c>
+      <c r="T447" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:14:17+00:00</t>
+        </is>
+      </c>
+      <c r="B448" t="n">
+        <v>304.95</v>
+      </c>
+      <c r="C448" t="n">
+        <v>303.58</v>
+      </c>
+      <c r="D448" t="n">
+        <v>303</v>
+      </c>
+      <c r="E448" t="n">
+        <v>310.69</v>
+      </c>
+      <c r="F448" t="n">
+        <v>323.99</v>
+      </c>
+      <c r="G448" t="n">
+        <v>317.64</v>
+      </c>
+      <c r="H448" t="n">
+        <v>314.21</v>
+      </c>
+      <c r="I448" t="n">
+        <v>310.52</v>
+      </c>
+      <c r="J448" t="n">
+        <v>320.92</v>
+      </c>
+      <c r="K448" t="n">
+        <v>333.21</v>
+      </c>
+      <c r="L448" t="n">
+        <v>332.28</v>
+      </c>
+      <c r="M448" t="n">
+        <v>331.98</v>
+      </c>
+      <c r="N448" t="n">
+        <v>327.22</v>
+      </c>
+      <c r="O448" t="n">
+        <v>319.54</v>
+      </c>
+      <c r="P448" t="n">
+        <v>321.52</v>
+      </c>
+      <c r="Q448" t="n">
+        <v>324.57</v>
+      </c>
+      <c r="R448" t="n">
+        <v>328.28</v>
+      </c>
+      <c r="S448" t="n">
+        <v>338.07</v>
+      </c>
+      <c r="T448" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:13:52+00:00</t>
+        </is>
+      </c>
+      <c r="B449" t="n">
+        <v>304.58</v>
+      </c>
+      <c r="C449" t="n">
+        <v>302.94</v>
+      </c>
+      <c r="D449" t="n">
+        <v>302.38</v>
+      </c>
+      <c r="E449" t="n">
+        <v>309.79</v>
+      </c>
+      <c r="F449" t="n">
+        <v>323.6</v>
+      </c>
+      <c r="G449" t="n">
+        <v>316.5</v>
+      </c>
+      <c r="H449" t="n">
+        <v>313.37</v>
+      </c>
+      <c r="I449" t="n">
+        <v>309.64</v>
+      </c>
+      <c r="J449" t="n">
+        <v>320.64</v>
+      </c>
+      <c r="K449" t="n">
+        <v>331</v>
+      </c>
+      <c r="L449" t="n">
+        <v>331.05</v>
+      </c>
+      <c r="M449" t="n">
+        <v>331.25</v>
+      </c>
+      <c r="N449" t="n">
+        <v>325.97</v>
+      </c>
+      <c r="O449" t="n">
+        <v>318.45</v>
+      </c>
+      <c r="P449" t="n">
+        <v>319.78</v>
+      </c>
+      <c r="Q449" t="n">
+        <v>322.81</v>
+      </c>
+      <c r="R449" t="n">
+        <v>327.67</v>
+      </c>
+      <c r="S449" t="n">
+        <v>337.87</v>
+      </c>
+      <c r="T449" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:19:54+00:00</t>
+        </is>
+      </c>
+      <c r="B450" t="n">
+        <v>305.52</v>
+      </c>
+      <c r="C450" t="n">
+        <v>303.75</v>
+      </c>
+      <c r="D450" t="n">
+        <v>304.01</v>
+      </c>
+      <c r="E450" t="n">
+        <v>310.59</v>
+      </c>
+      <c r="F450" t="n">
+        <v>324</v>
+      </c>
+      <c r="G450" t="n">
+        <v>317.42</v>
+      </c>
+      <c r="H450" t="n">
+        <v>314.98</v>
+      </c>
+      <c r="I450" t="n">
+        <v>311.28</v>
+      </c>
+      <c r="J450" t="n">
+        <v>320.7</v>
+      </c>
+      <c r="K450" t="n">
+        <v>331.55</v>
+      </c>
+      <c r="L450" t="n">
+        <v>332.37</v>
+      </c>
+      <c r="M450" t="n">
+        <v>333.25</v>
+      </c>
+      <c r="N450" t="n">
+        <v>327.42</v>
+      </c>
+      <c r="O450" t="n">
+        <v>319.77</v>
+      </c>
+      <c r="P450" t="n">
+        <v>320.39</v>
+      </c>
+      <c r="Q450" t="n">
+        <v>321.71</v>
+      </c>
+      <c r="R450" t="n">
+        <v>326.69</v>
+      </c>
+      <c r="S450" t="n">
+        <v>336.33</v>
+      </c>
+      <c r="T450" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -29814,7 +30144,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B456"/>
+  <dimension ref="A1:B461"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34377,6 +34707,56 @@
       </c>
       <c r="B456" t="n">
         <v>0.38</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B457" t="n">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B458" t="n">
+        <v>-0.21</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B459" t="n">
+        <v>-0.51</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B460" t="n">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B461" t="n">
+        <v>-0.3</v>
       </c>
     </row>
   </sheetData>
@@ -34545,28 +34925,28 @@
         <v>0.0503</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6809102160188234</v>
+        <v>0.6278983837819674</v>
       </c>
       <c r="J2" t="n">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="K2" t="n">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1952452592614182</v>
+        <v>0.166692904035832</v>
       </c>
       <c r="M2" t="n">
-        <v>7.93175929435571</v>
+        <v>8.12095858499123</v>
       </c>
       <c r="N2" t="n">
-        <v>106.9009502404258</v>
+        <v>111.85531351784</v>
       </c>
       <c r="O2" t="n">
-        <v>10.33929157343122</v>
+        <v>10.57616724138948</v>
       </c>
       <c r="P2" t="n">
-        <v>310.8625126454931</v>
+        <v>311.4133401979208</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34623,28 +35003,28 @@
         <v>0.0789</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6089505552492562</v>
+        <v>0.5534426420002374</v>
       </c>
       <c r="J3" t="n">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="K3" t="n">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="L3" t="n">
-        <v>0.09302301001962465</v>
+        <v>0.07756374151280243</v>
       </c>
       <c r="M3" t="n">
-        <v>10.81497580019948</v>
+        <v>11.01044512474577</v>
       </c>
       <c r="N3" t="n">
-        <v>202.2501077845839</v>
+        <v>206.7344117740627</v>
       </c>
       <c r="O3" t="n">
-        <v>14.22146644283155</v>
+        <v>14.37826177860393</v>
       </c>
       <c r="P3" t="n">
-        <v>311.9817924853615</v>
+        <v>312.5585501527962</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34701,28 +35081,28 @@
         <v>0.075</v>
       </c>
       <c r="I4" t="n">
-        <v>0.74177730017427</v>
+        <v>0.6759298665560155</v>
       </c>
       <c r="J4" t="n">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="K4" t="n">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1052014334736161</v>
+        <v>0.088104865003925</v>
       </c>
       <c r="M4" t="n">
-        <v>12.16284574218616</v>
+        <v>12.42263441428729</v>
       </c>
       <c r="N4" t="n">
-        <v>261.7999258525973</v>
+        <v>268.372618422184</v>
       </c>
       <c r="O4" t="n">
-        <v>16.18023256484891</v>
+        <v>16.38208223707182</v>
       </c>
       <c r="P4" t="n">
-        <v>312.3105346211659</v>
+        <v>312.9947115269038</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34779,28 +35159,28 @@
         <v>0.0822</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7011472966554018</v>
+        <v>0.6421373695272212</v>
       </c>
       <c r="J5" t="n">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="K5" t="n">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1347079559701457</v>
+        <v>0.1137683866283683</v>
       </c>
       <c r="M5" t="n">
-        <v>9.574069125641671</v>
+        <v>9.828539923061738</v>
       </c>
       <c r="N5" t="n">
-        <v>176.6472217210499</v>
+        <v>182.2936117836205</v>
       </c>
       <c r="O5" t="n">
-        <v>13.29086986322001</v>
+        <v>13.50161515462578</v>
       </c>
       <c r="P5" t="n">
-        <v>317.885811968896</v>
+        <v>318.4989540702819</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34857,28 +35237,28 @@
         <v>0.0634</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7476583004857625</v>
+        <v>0.708904409351259</v>
       </c>
       <c r="J6" t="n">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="K6" t="n">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2060274118644486</v>
+        <v>0.1889032867010245</v>
       </c>
       <c r="M6" t="n">
-        <v>7.935792077875973</v>
+        <v>8.040438921196161</v>
       </c>
       <c r="N6" t="n">
-        <v>121.2217020932262</v>
+        <v>123.1726147963995</v>
       </c>
       <c r="O6" t="n">
-        <v>11.01007275603691</v>
+        <v>11.09831585405639</v>
       </c>
       <c r="P6" t="n">
-        <v>321.3270539532163</v>
+        <v>321.7289975068495</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -34935,28 +35315,28 @@
         <v>0.0667</v>
       </c>
       <c r="I7" t="n">
-        <v>1.224089732260248</v>
+        <v>1.161840721727026</v>
       </c>
       <c r="J7" t="n">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="K7" t="n">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3346583496146439</v>
+        <v>0.3065626949735855</v>
       </c>
       <c r="M7" t="n">
-        <v>9.816441735082359</v>
+        <v>10.08104550606062</v>
       </c>
       <c r="N7" t="n">
-        <v>167.6343882146306</v>
+        <v>174.2957362360248</v>
       </c>
       <c r="O7" t="n">
-        <v>12.94736993426196</v>
+        <v>13.20211105225315</v>
       </c>
       <c r="P7" t="n">
-        <v>312.3649508348216</v>
+        <v>313.0105759750909</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -35013,28 +35393,28 @@
         <v>0.06909999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9944413532457116</v>
+        <v>0.9375890186359238</v>
       </c>
       <c r="J8" t="n">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="K8" t="n">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2867844541134295</v>
+        <v>0.2584610370108207</v>
       </c>
       <c r="M8" t="n">
-        <v>9.073579609657594</v>
+        <v>9.30619943426368</v>
       </c>
       <c r="N8" t="n">
-        <v>138.3939498683131</v>
+        <v>143.9692013147687</v>
       </c>
       <c r="O8" t="n">
-        <v>11.76409579476099</v>
+        <v>11.99871665282453</v>
       </c>
       <c r="P8" t="n">
-        <v>312.954082726717</v>
+        <v>313.5437274754473</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -35091,28 +35471,28 @@
         <v>0.0717</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8331182862586025</v>
+        <v>0.7751510393752067</v>
       </c>
       <c r="J9" t="n">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="K9" t="n">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2165980080529305</v>
+        <v>0.1890886041182249</v>
       </c>
       <c r="M9" t="n">
-        <v>9.258971689426978</v>
+        <v>9.503381530719603</v>
       </c>
       <c r="N9" t="n">
-        <v>141.2658232290358</v>
+        <v>147.0910992700112</v>
       </c>
       <c r="O9" t="n">
-        <v>11.88552999361138</v>
+        <v>12.12811194168372</v>
       </c>
       <c r="P9" t="n">
-        <v>314.0526814006905</v>
+        <v>314.6538904246727</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -35169,28 +35549,28 @@
         <v>0.0781</v>
       </c>
       <c r="I10" t="n">
-        <v>0.9521989175923576</v>
+        <v>0.9022416121151107</v>
       </c>
       <c r="J10" t="n">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="K10" t="n">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2925467357922797</v>
+        <v>0.2671074460440461</v>
       </c>
       <c r="M10" t="n">
-        <v>8.053719085362493</v>
+        <v>8.263972308433912</v>
       </c>
       <c r="N10" t="n">
-        <v>123.381891124418</v>
+        <v>127.4986831890241</v>
       </c>
       <c r="O10" t="n">
-        <v>11.10774014480074</v>
+        <v>11.29153148111558</v>
       </c>
       <c r="P10" t="n">
-        <v>318.0847849732875</v>
+        <v>318.6029332059633</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -35247,28 +35627,28 @@
         <v>0.06270000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>1.456140950793207</v>
+        <v>1.385781875985524</v>
       </c>
       <c r="J11" t="n">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="K11" t="n">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3140097100463096</v>
+        <v>0.2898097703687448</v>
       </c>
       <c r="M11" t="n">
-        <v>11.9040576235529</v>
+        <v>12.23051740455813</v>
       </c>
       <c r="N11" t="n">
-        <v>259.623589486754</v>
+        <v>267.5870602329469</v>
       </c>
       <c r="O11" t="n">
-        <v>16.11283927452744</v>
+        <v>16.35808852625963</v>
       </c>
       <c r="P11" t="n">
-        <v>325.4376412398141</v>
+        <v>326.1683180531667</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -35325,28 +35705,28 @@
         <v>0.1014</v>
       </c>
       <c r="I12" t="n">
-        <v>1.456298204088905</v>
+        <v>1.367714876939946</v>
       </c>
       <c r="J12" t="n">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="K12" t="n">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2720975777344823</v>
+        <v>0.2428550202638725</v>
       </c>
       <c r="M12" t="n">
-        <v>12.69572154303407</v>
+        <v>13.13316125179396</v>
       </c>
       <c r="N12" t="n">
-        <v>317.3715084635406</v>
+        <v>330.9885916427714</v>
       </c>
       <c r="O12" t="n">
-        <v>17.81492375688261</v>
+        <v>18.19309186594657</v>
       </c>
       <c r="P12" t="n">
-        <v>332.88755721662</v>
+        <v>333.8079899121162</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -35403,28 +35783,28 @@
         <v>0.0926</v>
       </c>
       <c r="I13" t="n">
-        <v>1.457870877914265</v>
+        <v>1.356292303421599</v>
       </c>
       <c r="J13" t="n">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="K13" t="n">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2480730198352556</v>
+        <v>0.2160041346871486</v>
       </c>
       <c r="M13" t="n">
-        <v>13.8328761055941</v>
+        <v>14.32481232423162</v>
       </c>
       <c r="N13" t="n">
-        <v>360.3736888650506</v>
+        <v>378.9206068466044</v>
       </c>
       <c r="O13" t="n">
-        <v>18.98351097308005</v>
+        <v>19.46588315095424</v>
       </c>
       <c r="P13" t="n">
-        <v>338.4879543838056</v>
+        <v>339.5434010517176</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -35481,28 +35861,28 @@
         <v>0.1059</v>
       </c>
       <c r="I14" t="n">
-        <v>1.377623897736714</v>
+        <v>1.267258387661756</v>
       </c>
       <c r="J14" t="n">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="K14" t="n">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1881988019892324</v>
+        <v>0.159723716367478</v>
       </c>
       <c r="M14" t="n">
-        <v>16.18236290981415</v>
+        <v>16.69173492473801</v>
       </c>
       <c r="N14" t="n">
-        <v>457.9446486323906</v>
+        <v>479.482730583797</v>
       </c>
       <c r="O14" t="n">
-        <v>21.39964132018083</v>
+        <v>21.89709411277663</v>
       </c>
       <c r="P14" t="n">
-        <v>338.9896139176514</v>
+        <v>340.1363578625425</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -35559,28 +35939,28 @@
         <v>0.0788</v>
       </c>
       <c r="I15" t="n">
-        <v>1.375174755870432</v>
+        <v>1.262435549262526</v>
       </c>
       <c r="J15" t="n">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="K15" t="n">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1598546625431109</v>
+        <v>0.1353979326904049</v>
       </c>
       <c r="M15" t="n">
-        <v>18.00890656864478</v>
+        <v>18.52793160523249</v>
       </c>
       <c r="N15" t="n">
-        <v>555.9858201540305</v>
+        <v>577.5805883983483</v>
       </c>
       <c r="O15" t="n">
-        <v>23.57935156347669</v>
+        <v>24.03290636602965</v>
       </c>
       <c r="P15" t="n">
-        <v>332.7820767008999</v>
+        <v>333.9534912059441</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -35637,28 +36017,28 @@
         <v>0.0936</v>
       </c>
       <c r="I16" t="n">
-        <v>1.465560804428758</v>
+        <v>1.35377755823646</v>
       </c>
       <c r="J16" t="n">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="K16" t="n">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1665376312131469</v>
+        <v>0.1432766985212024</v>
       </c>
       <c r="M16" t="n">
-        <v>18.61315063455025</v>
+        <v>19.15163020386136</v>
       </c>
       <c r="N16" t="n">
-        <v>601.312338266652</v>
+        <v>621.9415278028131</v>
       </c>
       <c r="O16" t="n">
-        <v>24.52167078864432</v>
+        <v>24.93875553837466</v>
       </c>
       <c r="P16" t="n">
-        <v>331.1163974463663</v>
+        <v>332.2778791270175</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -35715,28 +36095,28 @@
         <v>0.08169999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>1.837245401509773</v>
+        <v>1.726932253173371</v>
       </c>
       <c r="J17" t="n">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="K17" t="n">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2387156289473722</v>
+        <v>0.2139035474181777</v>
       </c>
       <c r="M17" t="n">
-        <v>18.59334270469257</v>
+        <v>19.12451006965705</v>
       </c>
       <c r="N17" t="n">
-        <v>599.6782429123623</v>
+        <v>619.4438244583716</v>
       </c>
       <c r="O17" t="n">
-        <v>24.48832870802665</v>
+        <v>24.88862841657554</v>
       </c>
       <c r="P17" t="n">
-        <v>323.2757693257729</v>
+        <v>324.4260207047183</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -35793,28 +36173,28 @@
         <v>0.1195</v>
       </c>
       <c r="I18" t="n">
-        <v>1.891998949408415</v>
+        <v>1.788482558311728</v>
       </c>
       <c r="J18" t="n">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="K18" t="n">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="L18" t="n">
-        <v>0.27761003049898</v>
+        <v>0.2520529797921368</v>
       </c>
       <c r="M18" t="n">
-        <v>17.47988331873368</v>
+        <v>18.00207702536694</v>
       </c>
       <c r="N18" t="n">
-        <v>521.0713010785098</v>
+        <v>538.6892889169649</v>
       </c>
       <c r="O18" t="n">
-        <v>22.82698624607528</v>
+        <v>23.20968093095993</v>
       </c>
       <c r="P18" t="n">
-        <v>323.6630486443581</v>
+        <v>324.7386527666147</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -35871,28 +36251,28 @@
         <v>0.1194</v>
       </c>
       <c r="I19" t="n">
-        <v>1.785025969520006</v>
+        <v>1.695549423595847</v>
       </c>
       <c r="J19" t="n">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="K19" t="n">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2746554224775748</v>
+        <v>0.2525132304671721</v>
       </c>
       <c r="M19" t="n">
-        <v>16.55991360834801</v>
+        <v>16.97635162189389</v>
       </c>
       <c r="N19" t="n">
-        <v>470.7215574431442</v>
+        <v>482.9811719040551</v>
       </c>
       <c r="O19" t="n">
-        <v>21.6961184879495</v>
+        <v>21.97683261764659</v>
       </c>
       <c r="P19" t="n">
-        <v>330.2518507734918</v>
+        <v>331.1815779544035</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -35930,7 +36310,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T445"/>
+  <dimension ref="A1:T450"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -81255,6 +81635,516 @@
         </is>
       </c>
     </row>
+    <row r="446">
+      <c r="A446" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:14:08+00:00</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>-46.3061242376335,169.9080945832067</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>-46.30644023402438,169.90732180529056</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>-46.306761301929576,169.90655347288455</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>-46.30715870443709,169.9058520220724</t>
+        </is>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>-46.30760653539799,169.90519475428277</t>
+        </is>
+      </c>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>-46.30788353990045,169.9043996440059</t>
+        </is>
+      </c>
+      <c r="H446" t="inlineStr">
+        <is>
+          <t>-46.30814469385602,169.90360478150996</t>
+        </is>
+      </c>
+      <c r="I446" t="inlineStr">
+        <is>
+          <t>-46.308388200803236,169.90278583540916</t>
+        </is>
+      </c>
+      <c r="J446" t="inlineStr">
+        <is>
+          <t>-46.308759483687055,169.9020444236009</t>
+        </is>
+      </c>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>-46.30913535030298,169.90130459941057</t>
+        </is>
+      </c>
+      <c r="L446" t="inlineStr">
+        <is>
+          <t>-46.30942016810435,169.9005043119911</t>
+        </is>
+      </c>
+      <c r="M446" t="inlineStr">
+        <is>
+          <t>-46.309741829242185,169.8997339839638</t>
+        </is>
+      </c>
+      <c r="N446" t="inlineStr">
+        <is>
+          <t>-46.31001856174598,169.89892795677346</t>
+        </is>
+      </c>
+      <c r="O446" t="inlineStr">
+        <is>
+          <t>-46.31029110945299,169.89813298238752</t>
+        </is>
+      </c>
+      <c r="P446" t="inlineStr">
+        <is>
+          <t>-46.310565709556485,169.89734390581802</t>
+        </is>
+      </c>
+      <c r="Q446" t="inlineStr">
+        <is>
+          <t>-46.310869489641796,169.89655900872606</t>
+        </is>
+      </c>
+      <c r="R446" t="inlineStr">
+        <is>
+          <t>-46.311187413433764,169.89578146137927</t>
+        </is>
+      </c>
+      <c r="S446" t="inlineStr">
+        <is>
+          <t>-46.31154524880395,169.89502994056758</t>
+        </is>
+      </c>
+      <c r="T446" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:17+00:00</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>-46.30611339839355,169.90808508629152</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>-46.30643177784746,169.90731439639404</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>-46.306758995690814,169.90655145228803</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>-46.307157858813405,169.9058512811893</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>-46.307601231015084,169.90519010693154</t>
+        </is>
+      </c>
+      <c r="G447" t="inlineStr">
+        <is>
+          <t>-46.30787922050173,169.9043961657322</t>
+        </is>
+      </c>
+      <c r="H447" t="inlineStr">
+        <is>
+          <t>-46.308146716725744,169.90360619775802</t>
+        </is>
+      </c>
+      <c r="I447" t="inlineStr">
+        <is>
+          <t>-46.30838640331996,169.90278464211192</t>
+        </is>
+      </c>
+      <c r="J447" t="inlineStr">
+        <is>
+          <t>-46.308754091223435,169.9020408437362</t>
+        </is>
+      </c>
+      <c r="K447" t="inlineStr">
+        <is>
+          <t>-46.3091284871726,169.90129974084772</t>
+        </is>
+      </c>
+      <c r="L447" t="inlineStr">
+        <is>
+          <t>-46.30941922424086,169.9005035568396</t>
+        </is>
+      </c>
+      <c r="M447" t="inlineStr">
+        <is>
+          <t>-46.309741519113444,169.8997337208925</t>
+        </is>
+      </c>
+      <c r="N447" t="inlineStr">
+        <is>
+          <t>-46.31002732291704,169.89893538848193</t>
+        </is>
+      </c>
+      <c r="O447" t="inlineStr">
+        <is>
+          <t>-46.310295009289135,169.8981359438147</t>
+        </is>
+      </c>
+      <c r="P447" t="inlineStr">
+        <is>
+          <t>-46.31058197073534,169.89735469332592</t>
+        </is>
+      </c>
+      <c r="Q447" t="inlineStr">
+        <is>
+          <t>-46.31087784912633,169.89656446010633</t>
+        </is>
+      </c>
+      <c r="R447" t="inlineStr">
+        <is>
+          <t>-46.311183397592124,169.89577884260467</t>
+        </is>
+      </c>
+      <c r="S447" t="inlineStr">
+        <is>
+          <t>-46.31153598775779,169.89502390140277</t>
+        </is>
+      </c>
+      <c r="T447" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:14:17+00:00</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>-46.30611616585912,169.9080875110355</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>-46.30644154088804,169.90732295030207</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>-46.3067729868722,169.90656371057634</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>-46.307168006297445,169.9058601717881</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>-46.307606151022426,169.90519441751817</t>
+        </is>
+      </c>
+      <c r="G448" t="inlineStr">
+        <is>
+          <t>-46.30788958705852,169.90440451359</t>
+        </is>
+      </c>
+      <c r="H448" t="inlineStr">
+        <is>
+          <t>-46.30815286624963,169.90361050315263</t>
+        </is>
+      </c>
+      <c r="I448" t="inlineStr">
+        <is>
+          <t>-46.30839481880977,169.90279022891315</t>
+        </is>
+      </c>
+      <c r="J448" t="inlineStr">
+        <is>
+          <t>-46.30875392781545,169.90204073525547</t>
+        </is>
+      </c>
+      <c r="K448" t="inlineStr">
+        <is>
+          <t>-46.3091291331143,169.90130019812415</t>
+        </is>
+      </c>
+      <c r="L448" t="inlineStr">
+        <is>
+          <t>-46.30942433683472,169.900507647244</t>
+        </is>
+      </c>
+      <c r="M448" t="inlineStr">
+        <is>
+          <t>-46.30975128816876,169.89974200764067</t>
+        </is>
+      </c>
+      <c r="N448" t="inlineStr">
+        <is>
+          <t>-46.31004282941342,169.89894854195393</t>
+        </is>
+      </c>
+      <c r="O448" t="inlineStr">
+        <is>
+          <t>-46.310307584270575,169.8981454929092</t>
+        </is>
+      </c>
+      <c r="P448" t="inlineStr">
+        <is>
+          <t>-46.31059684276748,169.89736455929338</t>
+        </is>
+      </c>
+      <c r="Q448" t="inlineStr">
+        <is>
+          <t>-46.31089178160006,169.89657354574368</t>
+        </is>
+      </c>
+      <c r="R448" t="inlineStr">
+        <is>
+          <t>-46.311192576658634,169.89578482837572</t>
+        </is>
+      </c>
+      <c r="S448" t="inlineStr">
+        <is>
+          <t>-46.31154319989997,169.895028604469</t>
+        </is>
+      </c>
+      <c r="T448" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:13:52+00:00</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>-46.306113321519504,169.90808501893753</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>-46.306436620930654,169.90731863967088</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>-46.3067682206457,169.90655953467524</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>-46.307161087558406,169.90585411001584</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>-46.307603152892966,169.90519179075437</t>
+        </is>
+      </c>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>-46.30788063412316,169.90439730407627</t>
+        </is>
+      </c>
+      <c r="H449" t="inlineStr">
+        <is>
+          <t>-46.30814606940744,169.9036057445586</t>
+        </is>
+      </c>
+      <c r="I449" t="inlineStr">
+        <is>
+          <t>-46.30838762887673,169.9027854557237</t>
+        </is>
+      </c>
+      <c r="J449" t="inlineStr">
+        <is>
+          <t>-46.308751640103566,169.90203921652517</t>
+        </is>
+      </c>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>-46.30911128897447,169.90128756586597</t>
+        </is>
+      </c>
+      <c r="L449" t="inlineStr">
+        <is>
+          <t>-46.309414662233934,169.90049990694092</t>
+        </is>
+      </c>
+      <c r="M449" t="inlineStr">
+        <is>
+          <t>-46.30974562831931,169.8997372065878</t>
+        </is>
+      </c>
+      <c r="N449" t="inlineStr">
+        <is>
+          <t>-46.31003313785334,169.89894032103308</t>
+        </is>
+      </c>
+      <c r="O449" t="inlineStr">
+        <is>
+          <t>-46.31029890912522,169.89813890524232</t>
+        </is>
+      </c>
+      <c r="P449" t="inlineStr">
+        <is>
+          <t>-46.31058262445105,169.8973551269947</t>
+        </is>
+      </c>
+      <c r="Q449" t="inlineStr">
+        <is>
+          <t>-46.31087735739195,169.89656413943686</t>
+        </is>
+      </c>
+      <c r="R449" t="inlineStr">
+        <is>
+          <t>-46.311187577345656,169.89578156826806</t>
+        </is>
+      </c>
+      <c r="S449" t="inlineStr">
+        <is>
+          <t>-46.31154156077675,169.8950275355902</t>
+        </is>
+      </c>
+      <c r="T449" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:19:54+00:00</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>-46.306120547679555,169.9080913502139</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>-46.30644284775169,169.9073240953136</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>-46.3067807512086,169.90657051325547</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>-46.30716723754867,169.9058594982578</t>
+        </is>
+      </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>-46.30760622789753,169.90519448487112</t>
+        </is>
+      </c>
+      <c r="G450" t="inlineStr">
+        <is>
+          <t>-46.30788785929909,169.90440312228017</t>
+        </is>
+      </c>
+      <c r="H450" t="inlineStr">
+        <is>
+          <t>-46.308159096688165,169.9036148651982</t>
+        </is>
+      </c>
+      <c r="I450" t="inlineStr">
+        <is>
+          <t>-46.30840102829726,169.90279435121414</t>
+        </is>
+      </c>
+      <c r="J450" t="inlineStr">
+        <is>
+          <t>-46.30875213032755,169.90203954196738</t>
+        </is>
+      </c>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>-46.309115729823866,169.90129070963988</t>
+        </is>
+      </c>
+      <c r="L450" t="inlineStr">
+        <is>
+          <t>-46.309425044732315,169.90050821360774</t>
+        </is>
+      </c>
+      <c r="M450" t="inlineStr">
+        <is>
+          <t>-46.309761134755725,169.89975036015963</t>
+        </is>
+      </c>
+      <c r="N450" t="inlineStr">
+        <is>
+          <t>-46.31004438006298,169.89894985730155</t>
+        </is>
+      </c>
+      <c r="O450" t="inlineStr">
+        <is>
+          <t>-46.31030941480578,169.89814688296764</t>
+        </is>
+      </c>
+      <c r="P450" t="inlineStr">
+        <is>
+          <t>-46.31058760903332,169.89735843371955</t>
+        </is>
+      </c>
+      <c r="Q450" t="inlineStr">
+        <is>
+          <t>-46.310868342261536,169.89655826049753</t>
+        </is>
+      </c>
+      <c r="R450" t="inlineStr">
+        <is>
+          <t>-46.31117954566235,169.8957763307192</t>
+        </is>
+      </c>
+      <c r="S450" t="inlineStr">
+        <is>
+          <t>-46.31152893952777,169.89501930522556</t>
+        </is>
+      </c>
+      <c r="T450" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0527/nzd0527.xlsx
+++ b/data/nzd0527/nzd0527.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T450"/>
+  <dimension ref="A1:T452"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30128,6 +30128,138 @@
         <v>336.33</v>
       </c>
       <c r="T450" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:03+00:00</t>
+        </is>
+      </c>
+      <c r="B451" t="n">
+        <v>305.63</v>
+      </c>
+      <c r="C451" t="n">
+        <v>303.12</v>
+      </c>
+      <c r="D451" t="n">
+        <v>303.26</v>
+      </c>
+      <c r="E451" t="n">
+        <v>309.8</v>
+      </c>
+      <c r="F451" t="n">
+        <v>323.55</v>
+      </c>
+      <c r="G451" t="n">
+        <v>316.04</v>
+      </c>
+      <c r="H451" t="n">
+        <v>313.18</v>
+      </c>
+      <c r="I451" t="n">
+        <v>309.61</v>
+      </c>
+      <c r="J451" t="n">
+        <v>319.87</v>
+      </c>
+      <c r="K451" t="n">
+        <v>329.21</v>
+      </c>
+      <c r="L451" t="n">
+        <v>332.37</v>
+      </c>
+      <c r="M451" t="n">
+        <v>331.21</v>
+      </c>
+      <c r="N451" t="n">
+        <v>325.83</v>
+      </c>
+      <c r="O451" t="n">
+        <v>317.05</v>
+      </c>
+      <c r="P451" t="n">
+        <v>316.73</v>
+      </c>
+      <c r="Q451" t="n">
+        <v>316.92</v>
+      </c>
+      <c r="R451" t="n">
+        <v>322.99</v>
+      </c>
+      <c r="S451" t="n">
+        <v>333.68</v>
+      </c>
+      <c r="T451" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:19:59+00:00</t>
+        </is>
+      </c>
+      <c r="B452" t="n">
+        <v>305.63</v>
+      </c>
+      <c r="C452" t="n">
+        <v>300.99</v>
+      </c>
+      <c r="D452" t="n">
+        <v>300.9</v>
+      </c>
+      <c r="E452" t="n">
+        <v>309.3</v>
+      </c>
+      <c r="F452" t="n">
+        <v>323.57</v>
+      </c>
+      <c r="G452" t="n">
+        <v>315.65</v>
+      </c>
+      <c r="H452" t="n">
+        <v>313.94</v>
+      </c>
+      <c r="I452" t="n">
+        <v>310.18</v>
+      </c>
+      <c r="J452" t="n">
+        <v>319.86</v>
+      </c>
+      <c r="K452" t="n">
+        <v>328.87</v>
+      </c>
+      <c r="L452" t="n">
+        <v>333.01</v>
+      </c>
+      <c r="M452" t="n">
+        <v>332.24</v>
+      </c>
+      <c r="N452" t="n">
+        <v>326.49</v>
+      </c>
+      <c r="O452" t="n">
+        <v>315.96</v>
+      </c>
+      <c r="P452" t="n">
+        <v>312.46</v>
+      </c>
+      <c r="Q452" t="n">
+        <v>311.49</v>
+      </c>
+      <c r="R452" t="n">
+        <v>319.3</v>
+      </c>
+      <c r="S452" t="n">
+        <v>333.68</v>
+      </c>
+      <c r="T452" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -30144,7 +30276,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B461"/>
+  <dimension ref="A1:B463"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34757,6 +34889,26 @@
       </c>
       <c r="B461" t="n">
         <v>-0.3</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B462" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B463" t="n">
+        <v>-1.06</v>
       </c>
     </row>
   </sheetData>
@@ -34925,28 +35077,28 @@
         <v>0.0503</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6278983837819674</v>
+        <v>0.6079382744237727</v>
       </c>
       <c r="J2" t="n">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="K2" t="n">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="L2" t="n">
-        <v>0.166692904035832</v>
+        <v>0.1566139945424609</v>
       </c>
       <c r="M2" t="n">
-        <v>8.12095858499123</v>
+        <v>8.19302505589344</v>
       </c>
       <c r="N2" t="n">
-        <v>111.85531351784</v>
+        <v>113.5967587386201</v>
       </c>
       <c r="O2" t="n">
-        <v>10.57616724138948</v>
+        <v>10.65817802152976</v>
       </c>
       <c r="P2" t="n">
-        <v>311.4133401979208</v>
+        <v>311.6217055995478</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -35003,28 +35155,28 @@
         <v>0.0789</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5534426420002374</v>
+        <v>0.5310817592493413</v>
       </c>
       <c r="J3" t="n">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="K3" t="n">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07756374151280243</v>
+        <v>0.07163337446059037</v>
       </c>
       <c r="M3" t="n">
-        <v>11.01044512474577</v>
+        <v>11.08956699231832</v>
       </c>
       <c r="N3" t="n">
-        <v>206.7344117740627</v>
+        <v>208.6306075998903</v>
       </c>
       <c r="O3" t="n">
-        <v>14.37826177860393</v>
+        <v>14.4440509414738</v>
       </c>
       <c r="P3" t="n">
-        <v>312.5585501527962</v>
+        <v>312.7919820100537</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -35081,28 +35233,28 @@
         <v>0.075</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6759298665560155</v>
+        <v>0.6503054319357761</v>
       </c>
       <c r="J4" t="n">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="K4" t="n">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="L4" t="n">
-        <v>0.088104865003925</v>
+        <v>0.08181717004820466</v>
       </c>
       <c r="M4" t="n">
-        <v>12.42263441428729</v>
+        <v>12.52279436630395</v>
       </c>
       <c r="N4" t="n">
-        <v>268.372618422184</v>
+        <v>270.8760575853836</v>
       </c>
       <c r="O4" t="n">
-        <v>16.38208223707182</v>
+        <v>16.4583127198806</v>
       </c>
       <c r="P4" t="n">
-        <v>312.9947115269038</v>
+        <v>313.2622123863766</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35159,28 +35311,28 @@
         <v>0.0822</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6421373695272212</v>
+        <v>0.6190526793953031</v>
       </c>
       <c r="J5" t="n">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="K5" t="n">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1137683866283683</v>
+        <v>0.1059984250874674</v>
       </c>
       <c r="M5" t="n">
-        <v>9.828539923061738</v>
+        <v>9.931859064878203</v>
       </c>
       <c r="N5" t="n">
-        <v>182.2936117836205</v>
+        <v>184.4782753277081</v>
       </c>
       <c r="O5" t="n">
-        <v>13.50161515462578</v>
+        <v>13.58227798742568</v>
       </c>
       <c r="P5" t="n">
-        <v>318.4989540702819</v>
+        <v>318.7399383233505</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35237,28 +35389,28 @@
         <v>0.0634</v>
       </c>
       <c r="I6" t="n">
-        <v>0.708904409351259</v>
+        <v>0.693760570753339</v>
       </c>
       <c r="J6" t="n">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="K6" t="n">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1889032867010245</v>
+        <v>0.1823083773147336</v>
       </c>
       <c r="M6" t="n">
-        <v>8.040438921196161</v>
+        <v>8.081210420082524</v>
       </c>
       <c r="N6" t="n">
-        <v>123.1726147963995</v>
+        <v>123.9212167145765</v>
       </c>
       <c r="O6" t="n">
-        <v>11.09831585405639</v>
+        <v>11.13199068965549</v>
       </c>
       <c r="P6" t="n">
-        <v>321.7289975068495</v>
+        <v>321.8868057053368</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -35315,28 +35467,28 @@
         <v>0.0667</v>
       </c>
       <c r="I7" t="n">
-        <v>1.161840721727026</v>
+        <v>1.13686921716395</v>
       </c>
       <c r="J7" t="n">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="K7" t="n">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3065626949735855</v>
+        <v>0.2953063983333131</v>
       </c>
       <c r="M7" t="n">
-        <v>10.08104550606062</v>
+        <v>10.18880325067948</v>
       </c>
       <c r="N7" t="n">
-        <v>174.2957362360248</v>
+        <v>177.0483995100762</v>
       </c>
       <c r="O7" t="n">
-        <v>13.20211105225315</v>
+        <v>13.30595353629631</v>
       </c>
       <c r="P7" t="n">
-        <v>313.0105759750909</v>
+        <v>313.2707954571505</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -35393,28 +35545,28 @@
         <v>0.06909999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9375890186359238</v>
+        <v>0.9154361848473946</v>
       </c>
       <c r="J8" t="n">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="K8" t="n">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2584610370108207</v>
+        <v>0.247698911150971</v>
       </c>
       <c r="M8" t="n">
-        <v>9.30619943426368</v>
+        <v>9.398552841783001</v>
       </c>
       <c r="N8" t="n">
-        <v>143.9692013147687</v>
+        <v>146.1057345107295</v>
       </c>
       <c r="O8" t="n">
-        <v>11.99871665282453</v>
+        <v>12.08742050690425</v>
       </c>
       <c r="P8" t="n">
-        <v>313.5437274754473</v>
+        <v>313.7745721898218</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -35471,28 +35623,28 @@
         <v>0.0717</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7751510393752067</v>
+        <v>0.7526325148145806</v>
       </c>
       <c r="J9" t="n">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="K9" t="n">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1890886041182249</v>
+        <v>0.1788385142025584</v>
       </c>
       <c r="M9" t="n">
-        <v>9.503381530719603</v>
+        <v>9.598339985427172</v>
       </c>
       <c r="N9" t="n">
-        <v>147.0910992700112</v>
+        <v>149.3059072806732</v>
       </c>
       <c r="O9" t="n">
-        <v>12.12811194168372</v>
+        <v>12.21907964130987</v>
       </c>
       <c r="P9" t="n">
-        <v>314.6538904246727</v>
+        <v>314.8885462576216</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -35549,28 +35701,28 @@
         <v>0.0781</v>
       </c>
       <c r="I10" t="n">
-        <v>0.9022416121151107</v>
+        <v>0.8820246114582861</v>
       </c>
       <c r="J10" t="n">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="K10" t="n">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2671074460440461</v>
+        <v>0.2568027841942299</v>
       </c>
       <c r="M10" t="n">
-        <v>8.263972308433912</v>
+        <v>8.347585856787729</v>
       </c>
       <c r="N10" t="n">
-        <v>127.4986831890241</v>
+        <v>129.2436671884959</v>
       </c>
       <c r="O10" t="n">
-        <v>11.29153148111558</v>
+        <v>11.3685384807589</v>
       </c>
       <c r="P10" t="n">
-        <v>318.6029332059633</v>
+        <v>318.813606991455</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -35627,28 +35779,28 @@
         <v>0.06270000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>1.385781875985524</v>
+        <v>1.355531296423854</v>
       </c>
       <c r="J11" t="n">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="K11" t="n">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2898097703687448</v>
+        <v>0.2789841505871942</v>
       </c>
       <c r="M11" t="n">
-        <v>12.23051740455813</v>
+        <v>12.37474546190658</v>
       </c>
       <c r="N11" t="n">
-        <v>267.5870602329469</v>
+        <v>271.5510087323321</v>
       </c>
       <c r="O11" t="n">
-        <v>16.35808852625963</v>
+        <v>16.47880483324965</v>
       </c>
       <c r="P11" t="n">
-        <v>326.1683180531667</v>
+        <v>326.4839320538586</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -35705,28 +35857,28 @@
         <v>0.1014</v>
       </c>
       <c r="I12" t="n">
-        <v>1.367714876939946</v>
+        <v>1.334366812322519</v>
       </c>
       <c r="J12" t="n">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="K12" t="n">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2428550202638725</v>
+        <v>0.2323435528618411</v>
       </c>
       <c r="M12" t="n">
-        <v>13.13316125179396</v>
+        <v>13.29308002099083</v>
       </c>
       <c r="N12" t="n">
-        <v>330.9885916427714</v>
+        <v>335.7669012170971</v>
       </c>
       <c r="O12" t="n">
-        <v>18.19309186594657</v>
+        <v>18.32394338610271</v>
       </c>
       <c r="P12" t="n">
-        <v>333.8079899121162</v>
+        <v>334.1561120532113</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -35783,28 +35935,28 @@
         <v>0.0926</v>
       </c>
       <c r="I13" t="n">
-        <v>1.356292303421599</v>
+        <v>1.317305205713387</v>
       </c>
       <c r="J13" t="n">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="K13" t="n">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2160041346871486</v>
+        <v>0.2042878599208692</v>
       </c>
       <c r="M13" t="n">
-        <v>14.32481232423162</v>
+        <v>14.51251493279306</v>
       </c>
       <c r="N13" t="n">
-        <v>378.9206068466044</v>
+        <v>385.7779354519379</v>
       </c>
       <c r="O13" t="n">
-        <v>19.46588315095424</v>
+        <v>19.64123049739852</v>
       </c>
       <c r="P13" t="n">
-        <v>339.5434010517176</v>
+        <v>339.950388735722</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -35861,28 +36013,28 @@
         <v>0.1059</v>
       </c>
       <c r="I14" t="n">
-        <v>1.267258387661756</v>
+        <v>1.2249455189769</v>
       </c>
       <c r="J14" t="n">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="K14" t="n">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="L14" t="n">
-        <v>0.159723716367478</v>
+        <v>0.1494478007647616</v>
       </c>
       <c r="M14" t="n">
-        <v>16.69173492473801</v>
+        <v>16.88134950701114</v>
       </c>
       <c r="N14" t="n">
-        <v>479.482730583797</v>
+        <v>487.4119057540268</v>
       </c>
       <c r="O14" t="n">
-        <v>21.89709411277663</v>
+        <v>22.0774071338558</v>
       </c>
       <c r="P14" t="n">
-        <v>340.1363578625425</v>
+        <v>340.5780643348542</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -35939,28 +36091,28 @@
         <v>0.0788</v>
       </c>
       <c r="I15" t="n">
-        <v>1.262435549262526</v>
+        <v>1.217174383817711</v>
       </c>
       <c r="J15" t="n">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="K15" t="n">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1353979326904049</v>
+        <v>0.1260027505245692</v>
       </c>
       <c r="M15" t="n">
-        <v>18.52793160523249</v>
+        <v>18.73151923014587</v>
       </c>
       <c r="N15" t="n">
-        <v>577.5805883983483</v>
+        <v>586.5253552159003</v>
       </c>
       <c r="O15" t="n">
-        <v>24.03290636602965</v>
+        <v>24.21828555484265</v>
       </c>
       <c r="P15" t="n">
-        <v>333.9534912059441</v>
+        <v>334.4259789758311</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -36017,28 +36169,28 @@
         <v>0.0936</v>
       </c>
       <c r="I16" t="n">
-        <v>1.35377755823646</v>
+        <v>1.306149024699013</v>
       </c>
       <c r="J16" t="n">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="K16" t="n">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1432766985212024</v>
+        <v>0.1335122601575851</v>
       </c>
       <c r="M16" t="n">
-        <v>19.15163020386136</v>
+        <v>19.3826956550691</v>
       </c>
       <c r="N16" t="n">
-        <v>621.9415278028131</v>
+        <v>631.9429575813311</v>
       </c>
       <c r="O16" t="n">
-        <v>24.93875553837466</v>
+        <v>25.13847564156051</v>
       </c>
       <c r="P16" t="n">
-        <v>332.2778791270175</v>
+        <v>332.7750868649023</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -36095,28 +36247,28 @@
         <v>0.08169999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>1.726932253173371</v>
+        <v>1.676862879018799</v>
       </c>
       <c r="J17" t="n">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="K17" t="n">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2139035474181777</v>
+        <v>0.2021720560702298</v>
       </c>
       <c r="M17" t="n">
-        <v>19.12451006965705</v>
+        <v>19.37299223737812</v>
       </c>
       <c r="N17" t="n">
-        <v>619.4438244583716</v>
+        <v>630.7244118723455</v>
       </c>
       <c r="O17" t="n">
-        <v>24.88862841657554</v>
+        <v>25.11422728001691</v>
       </c>
       <c r="P17" t="n">
-        <v>324.4260207047183</v>
+        <v>324.9505408567833</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -36173,28 +36325,28 @@
         <v>0.1195</v>
       </c>
       <c r="I18" t="n">
-        <v>1.788482558311728</v>
+        <v>1.742995624365057</v>
       </c>
       <c r="J18" t="n">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="K18" t="n">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2520529797921368</v>
+        <v>0.2403853400679032</v>
       </c>
       <c r="M18" t="n">
-        <v>18.00207702536694</v>
+        <v>18.23534487474489</v>
       </c>
       <c r="N18" t="n">
-        <v>538.6892889169649</v>
+        <v>547.9350675778445</v>
       </c>
       <c r="O18" t="n">
-        <v>23.20968093095993</v>
+        <v>23.40801289255123</v>
       </c>
       <c r="P18" t="n">
-        <v>324.7386527666147</v>
+        <v>325.2135029363469</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -36251,28 +36403,28 @@
         <v>0.1194</v>
       </c>
       <c r="I19" t="n">
-        <v>1.695549423595847</v>
+        <v>1.657636474091029</v>
       </c>
       <c r="J19" t="n">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="K19" t="n">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2525132304671721</v>
+        <v>0.2428682017821006</v>
       </c>
       <c r="M19" t="n">
-        <v>16.97635162189389</v>
+        <v>17.16040384202483</v>
       </c>
       <c r="N19" t="n">
-        <v>482.9811719040551</v>
+        <v>488.9118466301135</v>
       </c>
       <c r="O19" t="n">
-        <v>21.97683261764659</v>
+        <v>22.11135108106498</v>
       </c>
       <c r="P19" t="n">
-        <v>331.1815779544035</v>
+        <v>331.5773547148849</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -36310,7 +36462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T450"/>
+  <dimension ref="A1:T452"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -82145,6 +82297,210 @@
         </is>
       </c>
     </row>
+    <row r="451">
+      <c r="A451" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:03+00:00</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>-46.306121393294,169.90809209110805</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>-46.30643800466868,169.9073198520358</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>-46.30677498561228,169.90656546176086</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>-46.30716116443327,169.90585417736887</t>
+        </is>
+      </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>-46.3076027685174,169.9051914539898</t>
+        </is>
+      </c>
+      <c r="G451" t="inlineStr">
+        <is>
+          <t>-46.30787702153508,169.9043943949749</t>
+        </is>
+      </c>
+      <c r="H451" t="inlineStr">
+        <is>
+          <t>-46.30814453202643,169.90360466821014</t>
+        </is>
+      </c>
+      <c r="I451" t="inlineStr">
+        <is>
+          <t>-46.30838738376537,169.90278529300133</t>
+        </is>
+      </c>
+      <c r="J451" t="inlineStr">
+        <is>
+          <t>-46.30874534889582,169.90203504001758</t>
+        </is>
+      </c>
+      <c r="K451" t="inlineStr">
+        <is>
+          <t>-46.30909683602774,169.90127733431427</t>
+        </is>
+      </c>
+      <c r="L451" t="inlineStr">
+        <is>
+          <t>-46.309425044732315,169.90050821360774</t>
+        </is>
+      </c>
+      <c r="M451" t="inlineStr">
+        <is>
+          <t>-46.30974531819058,169.89973694351642</t>
+        </is>
+      </c>
+      <c r="N451" t="inlineStr">
+        <is>
+          <t>-46.31003205239856,169.89893940029012</t>
+        </is>
+      </c>
+      <c r="O451" t="inlineStr">
+        <is>
+          <t>-46.310287766736224,169.8981304440217</t>
+        </is>
+      </c>
+      <c r="P451" t="inlineStr">
+        <is>
+          <t>-46.310557701538414,169.8973385933792</t>
+        </is>
+      </c>
+      <c r="Q451" t="inlineStr">
+        <is>
+          <t>-46.31082908546327,169.89653266041086</t>
+        </is>
+      </c>
+      <c r="R451" t="inlineStr">
+        <is>
+          <t>-46.31114922195814,169.8957565563135</t>
+        </is>
+      </c>
+      <c r="S451" t="inlineStr">
+        <is>
+          <t>-46.31150722114354,169.8950051425937</t>
+        </is>
+      </c>
+      <c r="T451" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:19:59+00:00</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>-46.306121393294,169.90809209110805</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>-46.30642163043459,169.90730550572115</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>-46.306756843201256,169.90654956639807</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>-46.30715732068924,169.90585080971823</t>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>-46.30760292226763,169.90519158869563</t>
+        </is>
+      </c>
+      <c r="G452" t="inlineStr">
+        <is>
+          <t>-46.30787395868861,169.90439192856314</t>
+        </is>
+      </c>
+      <c r="H452" t="inlineStr">
+        <is>
+          <t>-46.30815068155038,169.90360897360443</t>
+        </is>
+      </c>
+      <c r="I452" t="inlineStr">
+        <is>
+          <t>-46.308392040881124,169.90278838472616</t>
+        </is>
+      </c>
+      <c r="J452" t="inlineStr">
+        <is>
+          <t>-46.30874526719183,169.90203498577722</t>
+        </is>
+      </c>
+      <c r="K452" t="inlineStr">
+        <is>
+          <t>-46.30909409077519,169.9012753908916</t>
+        </is>
+      </c>
+      <c r="L452" t="inlineStr">
+        <is>
+          <t>-46.30943007867072,169.90051224108367</t>
+        </is>
+      </c>
+      <c r="M452" t="inlineStr">
+        <is>
+          <t>-46.30975330400551,169.89974371760493</t>
+        </is>
+      </c>
+      <c r="N452" t="inlineStr">
+        <is>
+          <t>-46.31003716954239,169.89894374093583</t>
+        </is>
+      </c>
+      <c r="O452" t="inlineStr">
+        <is>
+          <t>-46.310279091590104,169.89812385635943</t>
+        </is>
+      </c>
+      <c r="P452" t="inlineStr">
+        <is>
+          <t>-46.31052280945717,169.897315446342</t>
+        </is>
+      </c>
+      <c r="Q452" t="inlineStr">
+        <is>
+          <t>-46.31078458349167,169.89650363989622</t>
+        </is>
+      </c>
+      <c r="R452" t="inlineStr">
+        <is>
+          <t>-46.311118980206885,169.89573683537324</t>
+        </is>
+      </c>
+      <c r="S452" t="inlineStr">
+        <is>
+          <t>-46.31150722114354,169.8950051425937</t>
+        </is>
+      </c>
+      <c r="T452" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
